--- a/clients/encore/testcases/search-for-product-groups/item-search-search-for-product-groups.xlsx
+++ b/clients/encore/testcases/search-for-product-groups/item-search-search-for-product-groups.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="341">
   <si>
     <t>TC ID</t>
   </si>
@@ -184,6 +184,48 @@
     <t>TC-ISR-PGR-005</t>
   </si>
   <si>
+    <t>An executed group search survives leaving and returning</t>
+  </si>
+  <si>
+    <t>The Product Groups page is open; the box is empty</t>
+  </si>
+  <si>
+    <t>1. Type Audio, click Search, note the count</t>
+  </si>
+  <si>
+    <t>Results load</t>
+  </si>
+  <si>
+    <t>2. Navigate away entirely, then return and wait for hydration</t>
+  </si>
+  <si>
+    <t>The box still holds `Audio`, the same count shows, and the rows are back</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-006</t>
+  </si>
+  <si>
+    <t>Result rows show their status</t>
+  </si>
+  <si>
+    <t>An Audio search has been executed with Active checked</t>
+  </si>
+  <si>
+    <t>1. Read the Status column of the visible rows</t>
+  </si>
+  <si>
+    <t>Every row shows `Active`</t>
+  </si>
+  <si>
+    <t>2. Read the Service Type column</t>
+  </si>
+  <si>
+    <t>Each row carries a service type (e.g. `Equipment Rental`)</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-007</t>
+  </si>
+  <si>
     <t>Reset clears the search and keeps the Active filter</t>
   </si>
   <si>
@@ -202,46 +244,801 @@
     <t>It remains checked</t>
   </si>
   <si>
+    <t>TC-ISR-PGR-008</t>
+  </si>
+  <si>
+    <t>The Enter key runs the group search</t>
+  </si>
+  <si>
+    <t>The Product Groups page is open with a clean search (Reset)</t>
+  </si>
+  <si>
+    <t>1. Type ZZ E2E, pause a moment, press Enter</t>
+  </si>
+  <si>
+    <t>The count label reports groups found and rows render — no click on Search was needed</t>
+  </si>
+  <si>
+    <t>2. Note the count, Reset, type the same word and click Search instead</t>
+  </si>
+  <si>
+    <t>The same count and the same first row come back</t>
+  </si>
+  <si>
     <t>TC-ISR-PGR-009</t>
   </si>
   <si>
-    <t>An executed group search survives leaving and returning</t>
-  </si>
-  <si>
-    <t>The Product Groups page is open; the box is empty</t>
-  </si>
-  <si>
-    <t>1. Type Audio, click Search, note the count</t>
-  </si>
-  <si>
-    <t>Results load</t>
-  </si>
-  <si>
-    <t>2. Navigate away entirely, then return and wait for hydration</t>
-  </si>
-  <si>
-    <t>The box still holds `Audio`, the same count shows, and the rows are back</t>
+    <t>The description column is searched too</t>
+  </si>
+  <si>
+    <t>Clean search; the automated groups exist (their descriptions start with "Automated group create check", their names do not contain that phrase)</t>
+  </si>
+  <si>
+    <t>1. Search Automated group create check</t>
+  </si>
+  <si>
+    <t>At least one group is found</t>
+  </si>
+  <si>
+    <t>2. Read every visible row</t>
+  </si>
+  <si>
+    <t>Each row's Description contains the phrase while its Name does not — the match came from the description</t>
   </si>
   <si>
     <t>TC-ISR-PGR-010</t>
   </si>
   <si>
-    <t>Result rows show their status</t>
-  </si>
-  <si>
-    <t>An Audio search has been executed with Active checked</t>
-  </si>
-  <si>
-    <t>1. Read the Status column of the visible rows</t>
-  </si>
-  <si>
-    <t>Every row shows `Active`</t>
-  </si>
-  <si>
-    <t>2. Read the Service Type column</t>
-  </si>
-  <si>
-    <t>Each row carries a service type (e.g. `Equipment Rental`)</t>
+    <t>Search ignores case and surrounding spaces; a spaces-only search counts as empty</t>
+  </si>
+  <si>
+    <t>Clean search</t>
+  </si>
+  <si>
+    <t>1. Search ZZ E2E and note the count</t>
+  </si>
+  <si>
+    <t>Groups are found (22 at verification)</t>
+  </si>
+  <si>
+    <t>2. Search zz e2e</t>
+  </si>
+  <si>
+    <t>The same count</t>
+  </si>
+  <si>
+    <t>3. Search ZZ E2E (three spaces either side)</t>
+  </si>
+  <si>
+    <t>The same count; the box keeps the spaces as typed</t>
+  </si>
+  <si>
+    <t>4. Search five spaces only</t>
+  </si>
+  <si>
+    <t>"0 product groups found" and "No results" — treated as an empty search</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-011</t>
+  </si>
+  <si>
+    <t>Search matches the typed words in order, as one phrase</t>
+  </si>
+  <si>
+    <t>Clean search; the group ZZ E2E Group 1788335968232 (description "Automated group create check 1788335968232") exists</t>
+  </si>
+  <si>
+    <t>1. Search Group 1788335968232</t>
+  </si>
+  <si>
+    <t>Exactly one row: `ZZ E2E Group 1788335968232`</t>
+  </si>
+  <si>
+    <t>2. Search 1788335968232 Group (the same words reversed)</t>
+  </si>
+  <si>
+    <t>"0 product groups found"</t>
+  </si>
+  <si>
+    <t>3. Search Group Automated (a word from the Name plus a word from the Description)</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-012</t>
+  </si>
+  <si>
+    <t>Special characters are searched literally</t>
+  </si>
+  <si>
+    <t>Clean search; the special-character groups (ZZ E2E Special &lt;b&gt;&amp;'"&lt;/b&gt;...) exist; at least one group name contains a literal %</t>
+  </si>
+  <si>
+    <t>1. Search &amp;'</t>
+  </si>
+  <si>
+    <t>Only groups whose Name or Description contains `&amp;'` are found (5 at verification), each row shows the characters verbatim</t>
+  </si>
+  <si>
+    <t>2. Search &lt;b&gt;</t>
+  </si>
+  <si>
+    <t>The same five groups</t>
+  </si>
+  <si>
+    <t>3. Search %</t>
+  </si>
+  <si>
+    <t>Only names containing a literal `%` come back (the "Caption … 80% …" groups) — `%` is not a wildcard, so the result is far smaller than the full catalog</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-013</t>
+  </si>
+  <si>
+    <t>A term matching nothing shows zero groups and "No results"; a 200-character term is accepted</t>
+  </si>
+  <si>
+    <t>1. Search zzzz-no-match-9f3</t>
+  </si>
+  <si>
+    <t>"0 product groups found", the "No results" placeholder, no rows, every pager button disabled, page box "1" with total "/ 1"</t>
+  </si>
+  <si>
+    <t>2. Search a 200-character term</t>
+  </si>
+  <si>
+    <t>The box holds all 200 characters (no maximum length); the same zero state, no error</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-014</t>
+  </si>
+  <si>
+    <t>A single match reports a count of 1 with one row</t>
+  </si>
+  <si>
+    <t>Clean search; the group ZZ E2E Group 1788335968232 exists</t>
+  </si>
+  <si>
+    <t>1. Search the full name ZZ E2E Group 1788335968232</t>
+  </si>
+  <si>
+    <t>The count is 1 and exactly one row renders, named as searched</t>
+  </si>
+  <si>
+    <t>2. Read the pager</t>
+  </si>
+  <si>
+    <t>Every pager button disabled, "1 / 1"</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-015</t>
+  </si>
+  <si>
+    <t>Names containing markup render as literal text</t>
+  </si>
+  <si>
+    <t>The special-character groups exist</t>
+  </si>
+  <si>
+    <t>1. Search &lt;b&gt;</t>
+  </si>
+  <si>
+    <t>Every row's Name shows the characters `&lt;b&gt;&amp;'"&lt;/b&gt;` verbatim — no bold text, no missing characters</t>
+  </si>
+  <si>
+    <t>2. Read the row's cell markup</t>
+  </si>
+  <si>
+    <t>The cell contains no `&lt;b&gt;` element; the angle brackets are text</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-016</t>
+  </si>
+  <si>
+    <t>A search submitted within the typing debounce runs the previous term (known defect)</t>
+  </si>
+  <si>
+    <t>A fresh page load with a clean search (no executed term stored)</t>
+  </si>
+  <si>
+    <t>1. Click the box, type ZZ E2E by keystrokes and press Enter immediately (no pause)</t>
+  </si>
+  <si>
+    <t>Intent: the typed term is searched and its groups are found. Today: the empty term is searched — "0 product groups found" with `ZZ E2E` still in the box</t>
+  </si>
+  <si>
+    <t>2. Search ZZ E2E properly (pause before Enter), then select all, type Audio and press Enter at once</t>
+  </si>
+  <si>
+    <t>Intent: the `Audio` groups. Today: the `ZZ E2E` rows stay while the box reads `Audio`</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-017</t>
+  </si>
+  <si>
+    <t>Clearing the Active filter lists inactive groups only</t>
+  </si>
+  <si>
+    <t>Clean search; inactive automated groups exist (ZZ E2E Inactive..., ZZ E2E Walk 2026-09-09 B)</t>
+  </si>
+  <si>
+    <t>1. Clear the Active checkbox and search ZZ E2E</t>
+  </si>
+  <si>
+    <t>Groups are found and every row's Status reads `Inactive`</t>
+  </si>
+  <si>
+    <t>2. Re-check Active and search again</t>
+  </si>
+  <si>
+    <t>Every row's Status reads `Active`; the count differs from step 1</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-018</t>
+  </si>
+  <si>
+    <t>The Active filter and its results survive a full reload</t>
+  </si>
+  <si>
+    <t>TC-017 state: Active cleared, ZZ E2E searched, inactive rows shown</t>
+  </si>
+  <si>
+    <t>1. Reload the page by address and wait for hydration</t>
+  </si>
+  <si>
+    <t>The box still holds `ZZ E2E`, Active is still cleared, the same inactive rows and count are back</t>
+  </si>
+  <si>
+    <t>2. Re-check Active, search, reload again</t>
+  </si>
+  <si>
+    <t>The active set is back with Active checked</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-019</t>
+  </si>
+  <si>
+    <t>Clicking a result row opens that group's Edit page</t>
+  </si>
+  <si>
+    <t>ZZ E2E searched; the first row is an automated group</t>
+  </si>
+  <si>
+    <t>1. Note the first row's Name and Description, then click its Description cell</t>
+  </si>
+  <si>
+    <t>The address becomes `…/product-groups/edit/&lt;id&gt;` and the heading reads "Edit"</t>
+  </si>
+  <si>
+    <t>2. Read the form</t>
+  </si>
+  <si>
+    <t>The Name box holds the row's name, the Description box the row's description, Active is checked, Save is disabled and Cancel enabled</t>
+  </si>
+  <si>
+    <t>3. Read the badge beside Active and the breadcrumb</t>
+  </si>
+  <si>
+    <t>A "Not Priced" (or "Priced") badge is shown; the breadcrumb reads Products › Product Groups</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-020</t>
+  </si>
+  <si>
+    <t>Returning from the Edit page restores the results and the page number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Product Groups"</t>
+  </si>
+  <si>
+    <t>ZZ E2E searched (more than 20 results); the grid moved to page 2</t>
+  </si>
+  <si>
+    <t>1. Click a row on page 2, then use the browser Back</t>
+  </si>
+  <si>
+    <t>The list shows the same count, page 2 with its rows, the box still holds `ZZ E2E`</t>
+  </si>
+  <si>
+    <t>2. Click a row again, then click the "Product Groups" breadcrumb on the Edit page</t>
+  </si>
+  <si>
+    <t>The same page-2 state comes back</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-021</t>
+  </si>
+  <si>
+    <t>The clear control empties the box but keeps the results</t>
+  </si>
+  <si>
+    <t>ZZ E2E searched</t>
+  </si>
+  <si>
+    <t>1. Read the search box</t>
+  </si>
+  <si>
+    <t>A clear (×) control shows inside the box while it holds text</t>
+  </si>
+  <si>
+    <t>2. Click the x</t>
+  </si>
+  <si>
+    <t>The box is empty; the count, the rows and the pager are unchanged; the × is gone</t>
+  </si>
+  <si>
+    <t>3. Type ZZ</t>
+  </si>
+  <si>
+    <t>The × reappears</t>
+  </si>
+  <si>
+    <t>4. Reload the page by address</t>
+  </si>
+  <si>
+    <t>The executed `ZZ E2E` search is restored — the × never touched the stored term</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-022</t>
+  </si>
+  <si>
+    <t>A loader shows in the search box while a search runs</t>
+  </si>
+  <si>
+    <t>1. Arm a watcher for the loader and the grid placeholders, type ZZ E2E, pause, press Enter</t>
+  </si>
+  <si>
+    <t>During the request a spinning loader renders inside the search panel and placeholder rows render in the grid</t>
+  </si>
+  <si>
+    <t>2. Wait for the rows</t>
+  </si>
+  <si>
+    <t>The loader and the placeholders are gone and the count is shown</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-023</t>
+  </si>
+  <si>
+    <t>The Products breadcrumb returns to the Products page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Products"</t>
+  </si>
+  <si>
+    <t>The Product Groups page is open</t>
+  </si>
+  <si>
+    <t>1. Click "Products" in the breadcrumb</t>
+  </si>
+  <si>
+    <t>The address is the Products page (`/locations/1101/products`) and its search panel renders</t>
+  </si>
+  <si>
+    <t>2. Use the browser Back</t>
+  </si>
+  <si>
+    <t>The Product Groups page returns with its last executed search restored</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-024</t>
+  </si>
+  <si>
+    <t>Last and first page jumps and the page-of-total label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Go to last page"
+Sample input 2: "Go to first page"</t>
+  </si>
+  <si>
+    <t>ZZ E2E searched at 20 rows per page (22 groups -&gt; 2 pages)</t>
+  </si>
+  <si>
+    <t>1. Read the pager</t>
+  </si>
+  <si>
+    <t>Page box "1", total "/ 2", first/previous disabled, next/last enabled</t>
+  </si>
+  <si>
+    <t>2. Click "Go to last page"</t>
+  </si>
+  <si>
+    <t>Page box "2", the remainder rows only (2 at verification), first/previous enabled, next/last disabled</t>
+  </si>
+  <si>
+    <t>Page box "1", 20 rows, the count label unchanged throughout</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-025</t>
+  </si>
+  <si>
+    <t>The page-number box jumps to a valid page and snaps back on invalid input</t>
+  </si>
+  <si>
+    <t>ZZ E2E searched, 2 pages, page 1 shown</t>
+  </si>
+  <si>
+    <t>1. Type 2 into the page box and press Enter</t>
+  </si>
+  <si>
+    <t>Page 2 renders (remainder rows, next/last disabled)</t>
+  </si>
+  <si>
+    <t>2. Type 9 and press Enter</t>
+  </si>
+  <si>
+    <t>The box snaps back to `2` and page 2 stays</t>
+  </si>
+  <si>
+    <t>3. Type 0 and press Enter</t>
+  </si>
+  <si>
+    <t>Same — back to `2`</t>
+  </si>
+  <si>
+    <t>4. Try to type abc</t>
+  </si>
+  <si>
+    <t>The box does not accept the letters (digits only)</t>
+  </si>
+  <si>
+    <t>5. Go to the first page, type 2, press Enter</t>
+  </si>
+  <si>
+    <t>Page 2 again</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-026</t>
+  </si>
+  <si>
+    <t>Rows per page offers 10 to 50 and reshapes the pages</t>
+  </si>
+  <si>
+    <t>ZZ E2E searched (22 groups at verification)</t>
+  </si>
+  <si>
+    <t>1. Open the rows-per-page selector</t>
+  </si>
+  <si>
+    <t>Options 10, 20, 30, 40, 50 with 20 selected</t>
+  </si>
+  <si>
+    <t>2. Choose 50</t>
+  </si>
+  <si>
+    <t>All groups on one page (22 rows), every pager button disabled, "1 / 1"</t>
+  </si>
+  <si>
+    <t>3. Choose 10</t>
+  </si>
+  <si>
+    <t>10 rows, "1 / 3", next/last enabled; "Go to last page" shows page 3 with the remainder</t>
+  </si>
+  <si>
+    <t>4. Choose 20 again</t>
+  </si>
+  <si>
+    <t>Back to a 20-row page</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-027</t>
+  </si>
+  <si>
+    <t>The chosen rows-per-page and page survive leaving and returning</t>
+  </si>
+  <si>
+    <t>ZZ E2E searched; rows per page set to 10; the grid moved to page 3</t>
+  </si>
+  <si>
+    <t>1. Click the "Products" breadcrumb, then use the browser Back</t>
+  </si>
+  <si>
+    <t>The list is back at 10 rows per page, page 3, with its rows and the same count</t>
+  </si>
+  <si>
+    <t>2. Navigate to the page by address</t>
+  </si>
+  <si>
+    <t>The same 10-per-page, page-3 state</t>
+  </si>
+  <si>
+    <t>3. Restore 20 rows per page</t>
+  </si>
+  <si>
+    <t>The pager reshapes to 2 pages</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-028</t>
+  </si>
+  <si>
+    <t>Reset from a later page returns the pager to page 1 of 1</t>
+  </si>
+  <si>
+    <t>ZZ E2E searched, 2 pages, the grid moved to page 2</t>
+  </si>
+  <si>
+    <t>The box clears, "0 product groups found", the page box reads "1" with total "/ 1", every pager button disabled</t>
+  </si>
+  <si>
+    <t>2. Search ZZ E2E again</t>
+  </si>
+  <si>
+    <t>Page 1 of 2 renders</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-029</t>
+  </si>
+  <si>
+    <t>Results default to Name ascending</t>
+  </si>
+  <si>
+    <t>Grid Options -&gt; Reset to Default View applied; ZZ E2E searched</t>
+  </si>
+  <si>
+    <t>1. Read the Name column on page 1</t>
+  </si>
+  <si>
+    <t>Every name is ≤ the next one (ascending by character code — `&lt;` sorts before `A`)</t>
+  </si>
+  <si>
+    <t>2. Read the header markers</t>
+  </si>
+  <si>
+    <t>The Name header shows the ascending arrow; Description and Service Type show the neutral (unsorted) marker; Status shows none</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-030</t>
+  </si>
+  <si>
+    <t>The Name column menu sorts descending and ascending</t>
+  </si>
+  <si>
+    <t>1. Open the Name column menu</t>
+  </si>
+  <si>
+    <t>Items: Sort ascending, Sort descending (Name cannot be hidden, so no Hide item)</t>
+  </si>
+  <si>
+    <t>2. Choose Sort descending</t>
+  </si>
+  <si>
+    <t>The names on page 1 now descend; the Name header shows the down arrow</t>
+  </si>
+  <si>
+    <t>3. Open the menu again and choose Sort ascending</t>
+  </si>
+  <si>
+    <t>The names ascend again; the up arrow shows</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-031</t>
+  </si>
+  <si>
+    <t>Description and Service Type sort through their column menus</t>
+  </si>
+  <si>
+    <t>ZZ E2E searched (two service types present at verification)</t>
+  </si>
+  <si>
+    <t>1. Open the Description menu and choose Sort descending</t>
+  </si>
+  <si>
+    <t>The Description column on page 1 descends; the arrow moves to the Description header and leaves Name</t>
+  </si>
+  <si>
+    <t>2. Open the Service Type menu and choose Sort ascending, then Sort descending</t>
+  </si>
+  <si>
+    <t>The Service Type column ascends, then descends; the arrow sits on Service Type</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-032</t>
+  </si>
+  <si>
+    <t>Sorting from a later page returns to page 1</t>
+  </si>
+  <si>
+    <t>The page box reads "1" and a full 20-row page renders in the new order</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-033</t>
+  </si>
+  <si>
+    <t>The applied sort survives a new search, a Reset and a reload</t>
+  </si>
+  <si>
+    <t>ZZ E2E searched and sorted by Service Type descending</t>
+  </si>
+  <si>
+    <t>1. Search ZZ E2E again</t>
+  </si>
+  <si>
+    <t>The rows are still Service Type descending; the arrow stays on Service Type</t>
+  </si>
+  <si>
+    <t>2. Click Reset, then search ZZ E2E</t>
+  </si>
+  <si>
+    <t>Still Service Type descending — the form Reset does not clear the sort</t>
+  </si>
+  <si>
+    <t>3. Reload the page by address</t>
+  </si>
+  <si>
+    <t>The sorted result set is restored</t>
+  </si>
+  <si>
+    <t>4. Grid Options</t>
+  </si>
+  <si>
+    <t>Name ascending is back</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-034</t>
+  </si>
+  <si>
+    <t>Every column header opens a sort menu and Escape closes it</t>
+  </si>
+  <si>
+    <t>1. Click the Name header cell</t>
+  </si>
+  <si>
+    <t>A menu opens with Sort ascending and Sort descending</t>
+  </si>
+  <si>
+    <t>2. Press Escape</t>
+  </si>
+  <si>
+    <t>The menu closes</t>
+  </si>
+  <si>
+    <t>3. Open the Description and Service Type menus in turn</t>
+  </si>
+  <si>
+    <t>Each lists Sort ascending, Sort descending, Hide column</t>
+  </si>
+  <si>
+    <t>4. Open the Status menu</t>
+  </si>
+  <si>
+    <t>It lists Hide column only — Status is not sortable and shows no sort icon</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-035</t>
+  </si>
+  <si>
+    <t>Grid Options hides and shows columns and remembers the choice</t>
+  </si>
+  <si>
+    <t>ZZ E2E searched, four columns shown</t>
+  </si>
+  <si>
+    <t>1. Open Grid Options</t>
+  </si>
+  <si>
+    <t>Reset to Default View plus checked toggles for Description, Service Type and Status (Name is not offered)</t>
+  </si>
+  <si>
+    <t>2. Uncheck Description and close the menu</t>
+  </si>
+  <si>
+    <t>Three headers remain: Name, Service Type, Status; the rows lose their description cell</t>
+  </si>
+  <si>
+    <t>Description is still hidden</t>
+  </si>
+  <si>
+    <t>4. Open Grid Options and check Description</t>
+  </si>
+  <si>
+    <t>Four columns again</t>
+  </si>
+  <si>
+    <t>5. Open the Service Type column menu and choose Hide column, then restore it through Grid Options</t>
+  </si>
+  <si>
+    <t>The column disappears and returns the same way</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-036</t>
+  </si>
+  <si>
+    <t>Reset to Default View restores columns, sort, page and stored preferences</t>
+  </si>
+  <si>
+    <t>ZZ E2E searched; Status hidden through Grid Options; Name sorted descending; the grid moved to page 2</t>
+  </si>
+  <si>
+    <t>1. Open Grid Options and choose Reset to Default View</t>
+  </si>
+  <si>
+    <t>All four columns are back, the Name header shows the ascending arrow and the names ascend, the page box reads "1", the results are kept</t>
+  </si>
+  <si>
+    <t>2. Read the stored grid preference</t>
+  </si>
+  <si>
+    <t>Column visibility, order and sizing are back to their defaults</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-037</t>
+  </si>
+  <si>
+    <t>Dragging a column header reorders the columns and the order persists</t>
+  </si>
+  <si>
+    <t>ZZ E2E searched; Reset to Default View applied</t>
+  </si>
+  <si>
+    <t>1. Drag the Name header's grip onto the Service Type header and release</t>
+  </si>
+  <si>
+    <t>The header order changes (Name moves right of Description at verification); the row cells follow</t>
+  </si>
+  <si>
+    <t>2. Reload the page by address</t>
+  </si>
+  <si>
+    <t>The new order is still in place</t>
+  </si>
+  <si>
+    <t>3. Grid Options</t>
+  </si>
+  <si>
+    <t>Name, Description, Service Type, Status again</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-038</t>
+  </si>
+  <si>
+    <t>Dragging a column edge resizes it and the width persists</t>
+  </si>
+  <si>
+    <t>1. Drag the Name column's resize handle 150 px to the right and release</t>
+  </si>
+  <si>
+    <t>The stored width for Name grows by 150 and the rendered Name header is wider than before</t>
+  </si>
+  <si>
+    <t>The Name header keeps its new width and the stored value is unchanged</t>
+  </si>
+  <si>
+    <t>The default width and an empty sizing preference are back</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-039</t>
+  </si>
+  <si>
+    <t>The search panel collapses and expands; the state is not remembered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Collapse search panel"
+Sample input 2: "Expand search panel"</t>
+  </si>
+  <si>
+    <t>1. Click the divider control "Collapse search panel"</t>
+  </si>
+  <si>
+    <t>The panel's container shrinks to zero width and the grid moves left and widens; the control is now named "Expand search panel"; the rows and count are untouched</t>
+  </si>
+  <si>
+    <t>The panel is open again ("Collapse search panel") — the collapsed state is not persisted</t>
+  </si>
+  <si>
+    <t>3. Collapse, then click "Expand search panel"</t>
+  </si>
+  <si>
+    <t>The panel and grid geometry are back to the original</t>
   </si>
   <si>
     <t>SUMMARY</t>
@@ -250,13 +1047,13 @@
     <t>Item Search — Search For Product Groups</t>
   </si>
   <si>
-    <t>Automated: 7 / Pending: 0</t>
-  </si>
-  <si>
-    <t>Pass:7 Fail:0 Skipped:0 Blocked:0</t>
-  </si>
-  <si>
-    <t>Last Updated: 2026-09-08</t>
+    <t>Automated: 39 / Pending: 0</t>
+  </si>
+  <si>
+    <t>Pass:39 Fail:0 Skipped:0 Blocked:0</t>
+  </si>
+  <si>
+    <t>Last Updated: 2026-09-10</t>
   </si>
 </sst>
 </file>
@@ -645,19 +1442,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="57" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="80" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="27" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
-    <col min="10" max="10" width="76" customWidth="1"/>
-    <col min="11" max="12" width="80" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="36" customWidth="1"/>
+    <col min="10" max="12" width="80" customWidth="1"/>
     <col min="13" max="13" width="26" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1358,45 +2154,3653 @@
         <v>25</v>
       </c>
     </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L18" t="s">
+        <v>79</v>
+      </c>
+      <c r="M18" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>79</v>
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" t="s">
+        <v>25</v>
+      </c>
+      <c r="K19" t="s">
+        <v>80</v>
+      </c>
+      <c r="L19" t="s">
+        <v>81</v>
+      </c>
+      <c r="M19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s">
+        <v>84</v>
+      </c>
+      <c r="K20" t="s">
+        <v>85</v>
+      </c>
+      <c r="L20" t="s">
+        <v>86</v>
+      </c>
+      <c r="M20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" t="s">
+        <v>87</v>
+      </c>
+      <c r="L21" t="s">
+        <v>88</v>
+      </c>
+      <c r="M21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>91</v>
+      </c>
+      <c r="K22" t="s">
+        <v>92</v>
+      </c>
+      <c r="L22" t="s">
+        <v>93</v>
+      </c>
+      <c r="M22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" t="s">
+        <v>94</v>
+      </c>
+      <c r="L23" t="s">
+        <v>95</v>
+      </c>
+      <c r="M23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I24" t="s">
+        <v>25</v>
+      </c>
+      <c r="J24" t="s">
+        <v>25</v>
+      </c>
+      <c r="K24" t="s">
+        <v>96</v>
+      </c>
+      <c r="L24" t="s">
+        <v>97</v>
+      </c>
+      <c r="M24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" t="s">
+        <v>25</v>
+      </c>
+      <c r="I25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J25" t="s">
+        <v>25</v>
+      </c>
+      <c r="K25" t="s">
+        <v>98</v>
+      </c>
+      <c r="L25" t="s">
+        <v>99</v>
+      </c>
+      <c r="M25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>102</v>
+      </c>
+      <c r="K26" t="s">
+        <v>103</v>
+      </c>
+      <c r="L26" t="s">
+        <v>104</v>
+      </c>
+      <c r="M26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" t="s">
+        <v>25</v>
+      </c>
+      <c r="I27" t="s">
+        <v>25</v>
+      </c>
+      <c r="J27" t="s">
+        <v>25</v>
+      </c>
+      <c r="K27" t="s">
+        <v>105</v>
+      </c>
+      <c r="L27" t="s">
+        <v>106</v>
+      </c>
+      <c r="M27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28" t="s">
+        <v>25</v>
+      </c>
+      <c r="J28" t="s">
+        <v>25</v>
+      </c>
+      <c r="K28" t="s">
+        <v>107</v>
+      </c>
+      <c r="L28" t="s">
+        <v>106</v>
+      </c>
+      <c r="M28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
+        <v>110</v>
+      </c>
+      <c r="K29" t="s">
+        <v>111</v>
+      </c>
+      <c r="L29" t="s">
+        <v>112</v>
+      </c>
+      <c r="M29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" t="s">
+        <v>25</v>
+      </c>
+      <c r="H30" t="s">
+        <v>25</v>
+      </c>
+      <c r="I30" t="s">
+        <v>25</v>
+      </c>
+      <c r="J30" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" t="s">
+        <v>113</v>
+      </c>
+      <c r="L30" t="s">
+        <v>114</v>
+      </c>
+      <c r="M30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" t="s">
+        <v>25</v>
+      </c>
+      <c r="I31" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" t="s">
+        <v>25</v>
+      </c>
+      <c r="K31" t="s">
+        <v>115</v>
+      </c>
+      <c r="L31" t="s">
+        <v>116</v>
+      </c>
+      <c r="M31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s">
+        <v>91</v>
+      </c>
+      <c r="K32" t="s">
+        <v>119</v>
+      </c>
+      <c r="L32" t="s">
+        <v>120</v>
+      </c>
+      <c r="M32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" t="s">
+        <v>25</v>
+      </c>
+      <c r="H33" t="s">
+        <v>25</v>
+      </c>
+      <c r="I33" t="s">
+        <v>25</v>
+      </c>
+      <c r="J33" t="s">
+        <v>25</v>
+      </c>
+      <c r="K33" t="s">
+        <v>121</v>
+      </c>
+      <c r="L33" t="s">
+        <v>122</v>
+      </c>
+      <c r="M33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s">
+        <v>125</v>
+      </c>
+      <c r="K34" t="s">
+        <v>126</v>
+      </c>
+      <c r="L34" t="s">
+        <v>127</v>
+      </c>
+      <c r="M34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35" t="s">
+        <v>25</v>
+      </c>
+      <c r="H35" t="s">
+        <v>25</v>
+      </c>
+      <c r="I35" t="s">
+        <v>25</v>
+      </c>
+      <c r="J35" t="s">
+        <v>25</v>
+      </c>
+      <c r="K35" t="s">
+        <v>128</v>
+      </c>
+      <c r="L35" t="s">
+        <v>129</v>
+      </c>
+      <c r="M35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>130</v>
+      </c>
+      <c r="B36" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s">
+        <v>132</v>
+      </c>
+      <c r="K36" t="s">
+        <v>133</v>
+      </c>
+      <c r="L36" t="s">
+        <v>134</v>
+      </c>
+      <c r="M36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" t="s">
+        <v>25</v>
+      </c>
+      <c r="G37" t="s">
+        <v>25</v>
+      </c>
+      <c r="H37" t="s">
+        <v>25</v>
+      </c>
+      <c r="I37" t="s">
+        <v>25</v>
+      </c>
+      <c r="J37" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" t="s">
+        <v>135</v>
+      </c>
+      <c r="L37" t="s">
+        <v>136</v>
+      </c>
+      <c r="M37" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>137</v>
+      </c>
+      <c r="B38" t="s">
+        <v>138</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s">
+        <v>139</v>
+      </c>
+      <c r="K38" t="s">
+        <v>140</v>
+      </c>
+      <c r="L38" t="s">
+        <v>141</v>
+      </c>
+      <c r="M38" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>25</v>
+      </c>
+      <c r="D39" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" t="s">
+        <v>25</v>
+      </c>
+      <c r="H39" t="s">
+        <v>25</v>
+      </c>
+      <c r="I39" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" t="s">
+        <v>25</v>
+      </c>
+      <c r="K39" t="s">
+        <v>142</v>
+      </c>
+      <c r="L39" t="s">
+        <v>143</v>
+      </c>
+      <c r="M39" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>146</v>
+      </c>
+      <c r="K40" t="s">
+        <v>147</v>
+      </c>
+      <c r="L40" t="s">
+        <v>148</v>
+      </c>
+      <c r="M40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" t="s">
+        <v>25</v>
+      </c>
+      <c r="H41" t="s">
+        <v>25</v>
+      </c>
+      <c r="I41" t="s">
+        <v>25</v>
+      </c>
+      <c r="J41" t="s">
+        <v>25</v>
+      </c>
+      <c r="K41" t="s">
+        <v>149</v>
+      </c>
+      <c r="L41" t="s">
+        <v>150</v>
+      </c>
+      <c r="M41" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>20</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>153</v>
+      </c>
+      <c r="K42" t="s">
+        <v>154</v>
+      </c>
+      <c r="L42" t="s">
+        <v>155</v>
+      </c>
+      <c r="M42" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" t="s">
+        <v>25</v>
+      </c>
+      <c r="H43" t="s">
+        <v>25</v>
+      </c>
+      <c r="I43" t="s">
+        <v>25</v>
+      </c>
+      <c r="J43" t="s">
+        <v>25</v>
+      </c>
+      <c r="K43" t="s">
+        <v>156</v>
+      </c>
+      <c r="L43" t="s">
+        <v>157</v>
+      </c>
+      <c r="M43" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>158</v>
+      </c>
+      <c r="B44" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s">
+        <v>160</v>
+      </c>
+      <c r="K44" t="s">
+        <v>161</v>
+      </c>
+      <c r="L44" t="s">
+        <v>162</v>
+      </c>
+      <c r="M44" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45" t="s">
+        <v>25</v>
+      </c>
+      <c r="H45" t="s">
+        <v>25</v>
+      </c>
+      <c r="I45" t="s">
+        <v>25</v>
+      </c>
+      <c r="J45" t="s">
+        <v>25</v>
+      </c>
+      <c r="K45" t="s">
+        <v>163</v>
+      </c>
+      <c r="L45" t="s">
+        <v>164</v>
+      </c>
+      <c r="M45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="s">
+        <v>25</v>
+      </c>
+      <c r="C46" t="s">
+        <v>25</v>
+      </c>
+      <c r="D46" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" t="s">
+        <v>25</v>
+      </c>
+      <c r="H46" t="s">
+        <v>25</v>
+      </c>
+      <c r="I46" t="s">
+        <v>25</v>
+      </c>
+      <c r="J46" t="s">
+        <v>25</v>
+      </c>
+      <c r="K46" t="s">
+        <v>165</v>
+      </c>
+      <c r="L46" t="s">
+        <v>166</v>
+      </c>
+      <c r="M46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>167</v>
+      </c>
+      <c r="B47" t="s">
+        <v>168</v>
+      </c>
+      <c r="C47" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" t="s">
+        <v>169</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s">
+        <v>170</v>
+      </c>
+      <c r="K47" t="s">
+        <v>171</v>
+      </c>
+      <c r="L47" t="s">
+        <v>172</v>
+      </c>
+      <c r="M47" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" t="s">
+        <v>25</v>
+      </c>
+      <c r="H48" t="s">
+        <v>25</v>
+      </c>
+      <c r="I48" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" t="s">
+        <v>25</v>
+      </c>
+      <c r="K48" t="s">
+        <v>173</v>
+      </c>
+      <c r="L48" t="s">
+        <v>174</v>
+      </c>
+      <c r="M48" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>175</v>
+      </c>
+      <c r="B49" t="s">
+        <v>176</v>
+      </c>
+      <c r="C49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s">
+        <v>177</v>
+      </c>
+      <c r="K49" t="s">
+        <v>178</v>
+      </c>
+      <c r="L49" t="s">
+        <v>179</v>
+      </c>
+      <c r="M49" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" t="s">
+        <v>25</v>
+      </c>
+      <c r="G50" t="s">
+        <v>25</v>
+      </c>
+      <c r="H50" t="s">
+        <v>25</v>
+      </c>
+      <c r="I50" t="s">
+        <v>25</v>
+      </c>
+      <c r="J50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K50" t="s">
+        <v>180</v>
+      </c>
+      <c r="L50" t="s">
+        <v>181</v>
+      </c>
+      <c r="M50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" t="s">
+        <v>25</v>
+      </c>
+      <c r="D51" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" t="s">
+        <v>25</v>
+      </c>
+      <c r="G51" t="s">
+        <v>25</v>
+      </c>
+      <c r="H51" t="s">
+        <v>25</v>
+      </c>
+      <c r="I51" t="s">
+        <v>25</v>
+      </c>
+      <c r="J51" t="s">
+        <v>25</v>
+      </c>
+      <c r="K51" t="s">
+        <v>182</v>
+      </c>
+      <c r="L51" t="s">
+        <v>183</v>
+      </c>
+      <c r="M51" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" t="s">
+        <v>25</v>
+      </c>
+      <c r="G52" t="s">
+        <v>25</v>
+      </c>
+      <c r="H52" t="s">
+        <v>25</v>
+      </c>
+      <c r="I52" t="s">
+        <v>25</v>
+      </c>
+      <c r="J52" t="s">
+        <v>25</v>
+      </c>
+      <c r="K52" t="s">
+        <v>184</v>
+      </c>
+      <c r="L52" t="s">
+        <v>185</v>
+      </c>
+      <c r="M52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>186</v>
+      </c>
+      <c r="B53" t="s">
+        <v>187</v>
+      </c>
+      <c r="C53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>91</v>
+      </c>
+      <c r="K53" t="s">
+        <v>188</v>
+      </c>
+      <c r="L53" t="s">
+        <v>189</v>
+      </c>
+      <c r="M53" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G54" t="s">
+        <v>25</v>
+      </c>
+      <c r="H54" t="s">
+        <v>25</v>
+      </c>
+      <c r="I54" t="s">
+        <v>25</v>
+      </c>
+      <c r="J54" t="s">
+        <v>25</v>
+      </c>
+      <c r="K54" t="s">
+        <v>190</v>
+      </c>
+      <c r="L54" t="s">
+        <v>191</v>
+      </c>
+      <c r="M54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>192</v>
+      </c>
+      <c r="B55" t="s">
+        <v>193</v>
+      </c>
+      <c r="C55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" t="s">
+        <v>194</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
+        <v>20</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s">
+        <v>195</v>
+      </c>
+      <c r="K55" t="s">
+        <v>196</v>
+      </c>
+      <c r="L55" t="s">
+        <v>197</v>
+      </c>
+      <c r="M55" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" t="s">
+        <v>25</v>
+      </c>
+      <c r="G56" t="s">
+        <v>25</v>
+      </c>
+      <c r="H56" t="s">
+        <v>25</v>
+      </c>
+      <c r="I56" t="s">
+        <v>25</v>
+      </c>
+      <c r="J56" t="s">
+        <v>25</v>
+      </c>
+      <c r="K56" t="s">
+        <v>198</v>
+      </c>
+      <c r="L56" t="s">
+        <v>199</v>
+      </c>
+      <c r="M56" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>200</v>
+      </c>
+      <c r="B57" t="s">
+        <v>201</v>
+      </c>
+      <c r="C57" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" t="s">
+        <v>202</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s">
+        <v>203</v>
+      </c>
+      <c r="K57" t="s">
+        <v>204</v>
+      </c>
+      <c r="L57" t="s">
+        <v>205</v>
+      </c>
+      <c r="M57" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" t="s">
+        <v>25</v>
+      </c>
+      <c r="G58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H58" t="s">
+        <v>25</v>
+      </c>
+      <c r="I58" t="s">
+        <v>25</v>
+      </c>
+      <c r="J58" t="s">
+        <v>25</v>
+      </c>
+      <c r="K58" t="s">
+        <v>206</v>
+      </c>
+      <c r="L58" t="s">
+        <v>207</v>
+      </c>
+      <c r="M58" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" t="s">
+        <v>25</v>
+      </c>
+      <c r="D59" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" t="s">
+        <v>25</v>
+      </c>
+      <c r="G59" t="s">
+        <v>25</v>
+      </c>
+      <c r="H59" t="s">
+        <v>25</v>
+      </c>
+      <c r="I59" t="s">
+        <v>25</v>
+      </c>
+      <c r="J59" t="s">
+        <v>25</v>
+      </c>
+      <c r="K59" t="s">
+        <v>52</v>
+      </c>
+      <c r="L59" t="s">
+        <v>208</v>
+      </c>
+      <c r="M59" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>209</v>
+      </c>
+      <c r="B60" t="s">
+        <v>210</v>
+      </c>
+      <c r="C60" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>211</v>
+      </c>
+      <c r="K60" t="s">
+        <v>212</v>
+      </c>
+      <c r="L60" t="s">
+        <v>213</v>
+      </c>
+      <c r="M60" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" t="s">
+        <v>25</v>
+      </c>
+      <c r="D61" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" t="s">
+        <v>25</v>
+      </c>
+      <c r="G61" t="s">
+        <v>25</v>
+      </c>
+      <c r="H61" t="s">
+        <v>25</v>
+      </c>
+      <c r="I61" t="s">
+        <v>25</v>
+      </c>
+      <c r="J61" t="s">
+        <v>25</v>
+      </c>
+      <c r="K61" t="s">
+        <v>214</v>
+      </c>
+      <c r="L61" t="s">
+        <v>215</v>
+      </c>
+      <c r="M61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" t="s">
+        <v>25</v>
+      </c>
+      <c r="D62" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" t="s">
+        <v>25</v>
+      </c>
+      <c r="G62" t="s">
+        <v>25</v>
+      </c>
+      <c r="H62" t="s">
+        <v>25</v>
+      </c>
+      <c r="I62" t="s">
+        <v>25</v>
+      </c>
+      <c r="J62" t="s">
+        <v>25</v>
+      </c>
+      <c r="K62" t="s">
+        <v>216</v>
+      </c>
+      <c r="L62" t="s">
+        <v>217</v>
+      </c>
+      <c r="M62" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" t="s">
+        <v>25</v>
+      </c>
+      <c r="C63" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" t="s">
+        <v>25</v>
+      </c>
+      <c r="G63" t="s">
+        <v>25</v>
+      </c>
+      <c r="H63" t="s">
+        <v>25</v>
+      </c>
+      <c r="I63" t="s">
+        <v>25</v>
+      </c>
+      <c r="J63" t="s">
+        <v>25</v>
+      </c>
+      <c r="K63" t="s">
+        <v>218</v>
+      </c>
+      <c r="L63" t="s">
+        <v>219</v>
+      </c>
+      <c r="M63" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64" t="s">
+        <v>25</v>
+      </c>
+      <c r="D64" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" t="s">
+        <v>25</v>
+      </c>
+      <c r="H64" t="s">
+        <v>25</v>
+      </c>
+      <c r="I64" t="s">
+        <v>25</v>
+      </c>
+      <c r="J64" t="s">
+        <v>25</v>
+      </c>
+      <c r="K64" t="s">
+        <v>220</v>
+      </c>
+      <c r="L64" t="s">
+        <v>221</v>
+      </c>
+      <c r="M64" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>222</v>
+      </c>
+      <c r="B65" t="s">
+        <v>223</v>
+      </c>
+      <c r="C65" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" t="s">
+        <v>16</v>
+      </c>
+      <c r="E65" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" t="s">
+        <v>20</v>
+      </c>
+      <c r="I65" t="s">
+        <v>21</v>
+      </c>
+      <c r="J65" t="s">
+        <v>224</v>
+      </c>
+      <c r="K65" t="s">
+        <v>225</v>
+      </c>
+      <c r="L65" t="s">
+        <v>226</v>
+      </c>
+      <c r="M65" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>25</v>
+      </c>
+      <c r="B66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" t="s">
+        <v>25</v>
+      </c>
+      <c r="D66" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" t="s">
+        <v>25</v>
+      </c>
+      <c r="G66" t="s">
+        <v>25</v>
+      </c>
+      <c r="H66" t="s">
+        <v>25</v>
+      </c>
+      <c r="I66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J66" t="s">
+        <v>25</v>
+      </c>
+      <c r="K66" t="s">
+        <v>227</v>
+      </c>
+      <c r="L66" t="s">
+        <v>228</v>
+      </c>
+      <c r="M66" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>25</v>
+      </c>
+      <c r="B67" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67" t="s">
+        <v>25</v>
+      </c>
+      <c r="D67" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67" t="s">
+        <v>25</v>
+      </c>
+      <c r="G67" t="s">
+        <v>25</v>
+      </c>
+      <c r="H67" t="s">
+        <v>25</v>
+      </c>
+      <c r="I67" t="s">
+        <v>25</v>
+      </c>
+      <c r="J67" t="s">
+        <v>25</v>
+      </c>
+      <c r="K67" t="s">
+        <v>229</v>
+      </c>
+      <c r="L67" t="s">
+        <v>230</v>
+      </c>
+      <c r="M67" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" t="s">
+        <v>25</v>
+      </c>
+      <c r="D68" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" t="s">
+        <v>25</v>
+      </c>
+      <c r="G68" t="s">
+        <v>25</v>
+      </c>
+      <c r="H68" t="s">
+        <v>25</v>
+      </c>
+      <c r="I68" t="s">
+        <v>25</v>
+      </c>
+      <c r="J68" t="s">
+        <v>25</v>
+      </c>
+      <c r="K68" t="s">
+        <v>231</v>
+      </c>
+      <c r="L68" t="s">
+        <v>232</v>
+      </c>
+      <c r="M68" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>233</v>
+      </c>
+      <c r="B69" t="s">
+        <v>234</v>
+      </c>
+      <c r="C69" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69" t="s">
+        <v>194</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" t="s">
+        <v>20</v>
+      </c>
+      <c r="I69" t="s">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s">
+        <v>235</v>
+      </c>
+      <c r="K69" t="s">
+        <v>236</v>
+      </c>
+      <c r="L69" t="s">
+        <v>237</v>
+      </c>
+      <c r="M69" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>25</v>
+      </c>
+      <c r="B70" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70" t="s">
+        <v>25</v>
+      </c>
+      <c r="D70" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" t="s">
+        <v>25</v>
+      </c>
+      <c r="F70" t="s">
+        <v>25</v>
+      </c>
+      <c r="G70" t="s">
+        <v>25</v>
+      </c>
+      <c r="H70" t="s">
+        <v>25</v>
+      </c>
+      <c r="I70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J70" t="s">
+        <v>25</v>
+      </c>
+      <c r="K70" t="s">
+        <v>238</v>
+      </c>
+      <c r="L70" t="s">
+        <v>239</v>
+      </c>
+      <c r="M70" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>25</v>
+      </c>
+      <c r="B71" t="s">
+        <v>25</v>
+      </c>
+      <c r="C71" t="s">
+        <v>25</v>
+      </c>
+      <c r="D71" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" t="s">
+        <v>25</v>
+      </c>
+      <c r="F71" t="s">
+        <v>25</v>
+      </c>
+      <c r="G71" t="s">
+        <v>25</v>
+      </c>
+      <c r="H71" t="s">
+        <v>25</v>
+      </c>
+      <c r="I71" t="s">
+        <v>25</v>
+      </c>
+      <c r="J71" t="s">
+        <v>25</v>
+      </c>
+      <c r="K71" t="s">
+        <v>240</v>
+      </c>
+      <c r="L71" t="s">
+        <v>241</v>
+      </c>
+      <c r="M71" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>242</v>
+      </c>
+      <c r="B72" t="s">
+        <v>243</v>
+      </c>
+      <c r="C72" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" t="s">
+        <v>20</v>
+      </c>
+      <c r="I72" t="s">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s">
+        <v>244</v>
+      </c>
+      <c r="K72" t="s">
+        <v>71</v>
+      </c>
+      <c r="L72" t="s">
+        <v>245</v>
+      </c>
+      <c r="M72" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" t="s">
+        <v>25</v>
+      </c>
+      <c r="C73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" t="s">
+        <v>25</v>
+      </c>
+      <c r="G73" t="s">
+        <v>25</v>
+      </c>
+      <c r="H73" t="s">
+        <v>25</v>
+      </c>
+      <c r="I73" t="s">
+        <v>25</v>
+      </c>
+      <c r="J73" t="s">
+        <v>25</v>
+      </c>
+      <c r="K73" t="s">
+        <v>246</v>
+      </c>
+      <c r="L73" t="s">
+        <v>247</v>
+      </c>
+      <c r="M73" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>248</v>
+      </c>
+      <c r="B74" t="s">
+        <v>249</v>
+      </c>
+      <c r="C74" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" t="s">
+        <v>16</v>
+      </c>
+      <c r="E74" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s">
+        <v>250</v>
+      </c>
+      <c r="K74" t="s">
+        <v>251</v>
+      </c>
+      <c r="L74" t="s">
+        <v>252</v>
+      </c>
+      <c r="M74" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>25</v>
+      </c>
+      <c r="B75" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75" t="s">
+        <v>25</v>
+      </c>
+      <c r="D75" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75" t="s">
+        <v>25</v>
+      </c>
+      <c r="F75" t="s">
+        <v>25</v>
+      </c>
+      <c r="G75" t="s">
+        <v>25</v>
+      </c>
+      <c r="H75" t="s">
+        <v>25</v>
+      </c>
+      <c r="I75" t="s">
+        <v>25</v>
+      </c>
+      <c r="J75" t="s">
+        <v>25</v>
+      </c>
+      <c r="K75" t="s">
+        <v>253</v>
+      </c>
+      <c r="L75" t="s">
+        <v>254</v>
+      </c>
+      <c r="M75" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>255</v>
+      </c>
+      <c r="B76" t="s">
+        <v>256</v>
+      </c>
+      <c r="C76" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" t="s">
+        <v>17</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" t="s">
+        <v>20</v>
+      </c>
+      <c r="I76" t="s">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s">
+        <v>177</v>
+      </c>
+      <c r="K76" t="s">
+        <v>257</v>
+      </c>
+      <c r="L76" t="s">
+        <v>258</v>
+      </c>
+      <c r="M76" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>25</v>
+      </c>
+      <c r="B77" t="s">
+        <v>25</v>
+      </c>
+      <c r="C77" t="s">
+        <v>25</v>
+      </c>
+      <c r="D77" t="s">
+        <v>25</v>
+      </c>
+      <c r="E77" t="s">
+        <v>25</v>
+      </c>
+      <c r="F77" t="s">
+        <v>25</v>
+      </c>
+      <c r="G77" t="s">
+        <v>25</v>
+      </c>
+      <c r="H77" t="s">
+        <v>25</v>
+      </c>
+      <c r="I77" t="s">
+        <v>25</v>
+      </c>
+      <c r="J77" t="s">
+        <v>25</v>
+      </c>
+      <c r="K77" t="s">
+        <v>259</v>
+      </c>
+      <c r="L77" t="s">
+        <v>260</v>
+      </c>
+      <c r="M77" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>25</v>
+      </c>
+      <c r="C78" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" t="s">
+        <v>25</v>
+      </c>
+      <c r="E78" t="s">
+        <v>25</v>
+      </c>
+      <c r="F78" t="s">
+        <v>25</v>
+      </c>
+      <c r="G78" t="s">
+        <v>25</v>
+      </c>
+      <c r="H78" t="s">
+        <v>25</v>
+      </c>
+      <c r="I78" t="s">
+        <v>25</v>
+      </c>
+      <c r="J78" t="s">
+        <v>25</v>
+      </c>
+      <c r="K78" t="s">
+        <v>261</v>
+      </c>
+      <c r="L78" t="s">
+        <v>262</v>
+      </c>
+      <c r="M78" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>263</v>
+      </c>
+      <c r="B79" t="s">
+        <v>264</v>
+      </c>
+      <c r="C79" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" t="s">
+        <v>17</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" t="s">
+        <v>20</v>
+      </c>
+      <c r="I79" t="s">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s">
+        <v>265</v>
+      </c>
+      <c r="K79" t="s">
+        <v>266</v>
+      </c>
+      <c r="L79" t="s">
+        <v>267</v>
+      </c>
+      <c r="M79" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" t="s">
+        <v>25</v>
+      </c>
+      <c r="C80" t="s">
+        <v>25</v>
+      </c>
+      <c r="D80" t="s">
+        <v>25</v>
+      </c>
+      <c r="E80" t="s">
+        <v>25</v>
+      </c>
+      <c r="F80" t="s">
+        <v>25</v>
+      </c>
+      <c r="G80" t="s">
+        <v>25</v>
+      </c>
+      <c r="H80" t="s">
+        <v>25</v>
+      </c>
+      <c r="I80" t="s">
+        <v>25</v>
+      </c>
+      <c r="J80" t="s">
+        <v>25</v>
+      </c>
+      <c r="K80" t="s">
+        <v>268</v>
+      </c>
+      <c r="L80" t="s">
+        <v>269</v>
+      </c>
+      <c r="M80" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>270</v>
+      </c>
+      <c r="B81" t="s">
+        <v>271</v>
+      </c>
+      <c r="C81" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" t="s">
+        <v>17</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" t="s">
+        <v>20</v>
+      </c>
+      <c r="I81" t="s">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s">
+        <v>244</v>
+      </c>
+      <c r="K81" t="s">
+        <v>266</v>
+      </c>
+      <c r="L81" t="s">
+        <v>272</v>
+      </c>
+      <c r="M81" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>273</v>
+      </c>
+      <c r="B82" t="s">
+        <v>274</v>
+      </c>
+      <c r="C82" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82" t="s">
+        <v>17</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" t="s">
+        <v>20</v>
+      </c>
+      <c r="I82" t="s">
+        <v>21</v>
+      </c>
+      <c r="J82" t="s">
+        <v>275</v>
+      </c>
+      <c r="K82" t="s">
+        <v>276</v>
+      </c>
+      <c r="L82" t="s">
+        <v>277</v>
+      </c>
+      <c r="M82" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B83" t="s">
+        <v>25</v>
+      </c>
+      <c r="C83" t="s">
+        <v>25</v>
+      </c>
+      <c r="D83" t="s">
+        <v>25</v>
+      </c>
+      <c r="E83" t="s">
+        <v>25</v>
+      </c>
+      <c r="F83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G83" t="s">
+        <v>25</v>
+      </c>
+      <c r="H83" t="s">
+        <v>25</v>
+      </c>
+      <c r="I83" t="s">
+        <v>25</v>
+      </c>
+      <c r="J83" t="s">
+        <v>25</v>
+      </c>
+      <c r="K83" t="s">
+        <v>278</v>
+      </c>
+      <c r="L83" t="s">
+        <v>279</v>
+      </c>
+      <c r="M83" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>25</v>
+      </c>
+      <c r="B84" t="s">
+        <v>25</v>
+      </c>
+      <c r="C84" t="s">
+        <v>25</v>
+      </c>
+      <c r="D84" t="s">
+        <v>25</v>
+      </c>
+      <c r="E84" t="s">
+        <v>25</v>
+      </c>
+      <c r="F84" t="s">
+        <v>25</v>
+      </c>
+      <c r="G84" t="s">
+        <v>25</v>
+      </c>
+      <c r="H84" t="s">
+        <v>25</v>
+      </c>
+      <c r="I84" t="s">
+        <v>25</v>
+      </c>
+      <c r="J84" t="s">
+        <v>25</v>
+      </c>
+      <c r="K84" t="s">
+        <v>280</v>
+      </c>
+      <c r="L84" t="s">
+        <v>281</v>
+      </c>
+      <c r="M84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>25</v>
+      </c>
+      <c r="B85" t="s">
+        <v>25</v>
+      </c>
+      <c r="C85" t="s">
+        <v>25</v>
+      </c>
+      <c r="D85" t="s">
+        <v>25</v>
+      </c>
+      <c r="E85" t="s">
+        <v>25</v>
+      </c>
+      <c r="F85" t="s">
+        <v>25</v>
+      </c>
+      <c r="G85" t="s">
+        <v>25</v>
+      </c>
+      <c r="H85" t="s">
+        <v>25</v>
+      </c>
+      <c r="I85" t="s">
+        <v>25</v>
+      </c>
+      <c r="J85" t="s">
+        <v>25</v>
+      </c>
+      <c r="K85" t="s">
+        <v>282</v>
+      </c>
+      <c r="L85" t="s">
+        <v>283</v>
+      </c>
+      <c r="M85" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>284</v>
+      </c>
+      <c r="B86" t="s">
+        <v>285</v>
+      </c>
+      <c r="C86" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" t="s">
+        <v>16</v>
+      </c>
+      <c r="E86" t="s">
+        <v>17</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>19</v>
+      </c>
+      <c r="H86" t="s">
+        <v>20</v>
+      </c>
+      <c r="I86" t="s">
+        <v>21</v>
+      </c>
+      <c r="J86" t="s">
+        <v>177</v>
+      </c>
+      <c r="K86" t="s">
+        <v>286</v>
+      </c>
+      <c r="L86" t="s">
+        <v>287</v>
+      </c>
+      <c r="M86" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" t="s">
+        <v>25</v>
+      </c>
+      <c r="C87" t="s">
+        <v>25</v>
+      </c>
+      <c r="D87" t="s">
+        <v>25</v>
+      </c>
+      <c r="E87" t="s">
+        <v>25</v>
+      </c>
+      <c r="F87" t="s">
+        <v>25</v>
+      </c>
+      <c r="G87" t="s">
+        <v>25</v>
+      </c>
+      <c r="H87" t="s">
+        <v>25</v>
+      </c>
+      <c r="I87" t="s">
+        <v>25</v>
+      </c>
+      <c r="J87" t="s">
+        <v>25</v>
+      </c>
+      <c r="K87" t="s">
+        <v>288</v>
+      </c>
+      <c r="L87" t="s">
+        <v>289</v>
+      </c>
+      <c r="M87" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>25</v>
+      </c>
+      <c r="B88" t="s">
+        <v>25</v>
+      </c>
+      <c r="C88" t="s">
+        <v>25</v>
+      </c>
+      <c r="D88" t="s">
+        <v>25</v>
+      </c>
+      <c r="E88" t="s">
+        <v>25</v>
+      </c>
+      <c r="F88" t="s">
+        <v>25</v>
+      </c>
+      <c r="G88" t="s">
+        <v>25</v>
+      </c>
+      <c r="H88" t="s">
+        <v>25</v>
+      </c>
+      <c r="I88" t="s">
+        <v>25</v>
+      </c>
+      <c r="J88" t="s">
+        <v>25</v>
+      </c>
+      <c r="K88" t="s">
+        <v>290</v>
+      </c>
+      <c r="L88" t="s">
+        <v>291</v>
+      </c>
+      <c r="M88" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" t="s">
+        <v>25</v>
+      </c>
+      <c r="C89" t="s">
+        <v>25</v>
+      </c>
+      <c r="D89" t="s">
+        <v>25</v>
+      </c>
+      <c r="E89" t="s">
+        <v>25</v>
+      </c>
+      <c r="F89" t="s">
+        <v>25</v>
+      </c>
+      <c r="G89" t="s">
+        <v>25</v>
+      </c>
+      <c r="H89" t="s">
+        <v>25</v>
+      </c>
+      <c r="I89" t="s">
+        <v>25</v>
+      </c>
+      <c r="J89" t="s">
+        <v>25</v>
+      </c>
+      <c r="K89" t="s">
+        <v>292</v>
+      </c>
+      <c r="L89" t="s">
+        <v>293</v>
+      </c>
+      <c r="M89" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>294</v>
+      </c>
+      <c r="B90" t="s">
+        <v>295</v>
+      </c>
+      <c r="C90" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" t="s">
+        <v>17</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" t="s">
+        <v>20</v>
+      </c>
+      <c r="I90" t="s">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s">
+        <v>296</v>
+      </c>
+      <c r="K90" t="s">
+        <v>297</v>
+      </c>
+      <c r="L90" t="s">
+        <v>298</v>
+      </c>
+      <c r="M90" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91" t="s">
+        <v>25</v>
+      </c>
+      <c r="C91" t="s">
+        <v>25</v>
+      </c>
+      <c r="D91" t="s">
+        <v>25</v>
+      </c>
+      <c r="E91" t="s">
+        <v>25</v>
+      </c>
+      <c r="F91" t="s">
+        <v>25</v>
+      </c>
+      <c r="G91" t="s">
+        <v>25</v>
+      </c>
+      <c r="H91" t="s">
+        <v>25</v>
+      </c>
+      <c r="I91" t="s">
+        <v>25</v>
+      </c>
+      <c r="J91" t="s">
+        <v>25</v>
+      </c>
+      <c r="K91" t="s">
+        <v>299</v>
+      </c>
+      <c r="L91" t="s">
+        <v>300</v>
+      </c>
+      <c r="M91" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>25</v>
+      </c>
+      <c r="B92" t="s">
+        <v>25</v>
+      </c>
+      <c r="C92" t="s">
+        <v>25</v>
+      </c>
+      <c r="D92" t="s">
+        <v>25</v>
+      </c>
+      <c r="E92" t="s">
+        <v>25</v>
+      </c>
+      <c r="F92" t="s">
+        <v>25</v>
+      </c>
+      <c r="G92" t="s">
+        <v>25</v>
+      </c>
+      <c r="H92" t="s">
+        <v>25</v>
+      </c>
+      <c r="I92" t="s">
+        <v>25</v>
+      </c>
+      <c r="J92" t="s">
+        <v>25</v>
+      </c>
+      <c r="K92" t="s">
+        <v>280</v>
+      </c>
+      <c r="L92" t="s">
+        <v>301</v>
+      </c>
+      <c r="M92" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>25</v>
+      </c>
+      <c r="B93" t="s">
+        <v>25</v>
+      </c>
+      <c r="C93" t="s">
+        <v>25</v>
+      </c>
+      <c r="D93" t="s">
+        <v>25</v>
+      </c>
+      <c r="E93" t="s">
+        <v>25</v>
+      </c>
+      <c r="F93" t="s">
+        <v>25</v>
+      </c>
+      <c r="G93" t="s">
+        <v>25</v>
+      </c>
+      <c r="H93" t="s">
+        <v>25</v>
+      </c>
+      <c r="I93" t="s">
+        <v>25</v>
+      </c>
+      <c r="J93" t="s">
+        <v>25</v>
+      </c>
+      <c r="K93" t="s">
+        <v>302</v>
+      </c>
+      <c r="L93" t="s">
+        <v>303</v>
+      </c>
+      <c r="M93" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>25</v>
+      </c>
+      <c r="B94" t="s">
+        <v>25</v>
+      </c>
+      <c r="C94" t="s">
+        <v>25</v>
+      </c>
+      <c r="D94" t="s">
+        <v>25</v>
+      </c>
+      <c r="E94" t="s">
+        <v>25</v>
+      </c>
+      <c r="F94" t="s">
+        <v>25</v>
+      </c>
+      <c r="G94" t="s">
+        <v>25</v>
+      </c>
+      <c r="H94" t="s">
+        <v>25</v>
+      </c>
+      <c r="I94" t="s">
+        <v>25</v>
+      </c>
+      <c r="J94" t="s">
+        <v>25</v>
+      </c>
+      <c r="K94" t="s">
+        <v>304</v>
+      </c>
+      <c r="L94" t="s">
+        <v>305</v>
+      </c>
+      <c r="M94" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>306</v>
+      </c>
+      <c r="B95" t="s">
+        <v>307</v>
+      </c>
+      <c r="C95" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" t="s">
+        <v>16</v>
+      </c>
+      <c r="E95" t="s">
+        <v>17</v>
+      </c>
+      <c r="F95" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" t="s">
+        <v>19</v>
+      </c>
+      <c r="H95" t="s">
+        <v>20</v>
+      </c>
+      <c r="I95" t="s">
+        <v>21</v>
+      </c>
+      <c r="J95" t="s">
+        <v>308</v>
+      </c>
+      <c r="K95" t="s">
+        <v>309</v>
+      </c>
+      <c r="L95" t="s">
+        <v>310</v>
+      </c>
+      <c r="M95" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>25</v>
+      </c>
+      <c r="B96" t="s">
+        <v>25</v>
+      </c>
+      <c r="C96" t="s">
+        <v>25</v>
+      </c>
+      <c r="D96" t="s">
+        <v>25</v>
+      </c>
+      <c r="E96" t="s">
+        <v>25</v>
+      </c>
+      <c r="F96" t="s">
+        <v>25</v>
+      </c>
+      <c r="G96" t="s">
+        <v>25</v>
+      </c>
+      <c r="H96" t="s">
+        <v>25</v>
+      </c>
+      <c r="I96" t="s">
+        <v>25</v>
+      </c>
+      <c r="J96" t="s">
+        <v>25</v>
+      </c>
+      <c r="K96" t="s">
+        <v>311</v>
+      </c>
+      <c r="L96" t="s">
+        <v>312</v>
+      </c>
+      <c r="M96" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>313</v>
+      </c>
+      <c r="B97" t="s">
+        <v>314</v>
+      </c>
+      <c r="C97" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97" t="s">
+        <v>16</v>
+      </c>
+      <c r="E97" t="s">
+        <v>17</v>
+      </c>
+      <c r="F97" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" t="s">
+        <v>19</v>
+      </c>
+      <c r="H97" t="s">
+        <v>20</v>
+      </c>
+      <c r="I97" t="s">
+        <v>21</v>
+      </c>
+      <c r="J97" t="s">
+        <v>315</v>
+      </c>
+      <c r="K97" t="s">
+        <v>316</v>
+      </c>
+      <c r="L97" t="s">
+        <v>317</v>
+      </c>
+      <c r="M97" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>25</v>
+      </c>
+      <c r="B98" t="s">
+        <v>25</v>
+      </c>
+      <c r="C98" t="s">
+        <v>25</v>
+      </c>
+      <c r="D98" t="s">
+        <v>25</v>
+      </c>
+      <c r="E98" t="s">
+        <v>25</v>
+      </c>
+      <c r="F98" t="s">
+        <v>25</v>
+      </c>
+      <c r="G98" t="s">
+        <v>25</v>
+      </c>
+      <c r="H98" t="s">
+        <v>25</v>
+      </c>
+      <c r="I98" t="s">
+        <v>25</v>
+      </c>
+      <c r="J98" t="s">
+        <v>25</v>
+      </c>
+      <c r="K98" t="s">
+        <v>318</v>
+      </c>
+      <c r="L98" t="s">
+        <v>319</v>
+      </c>
+      <c r="M98" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>25</v>
+      </c>
+      <c r="B99" t="s">
+        <v>25</v>
+      </c>
+      <c r="C99" t="s">
+        <v>25</v>
+      </c>
+      <c r="D99" t="s">
+        <v>25</v>
+      </c>
+      <c r="E99" t="s">
+        <v>25</v>
+      </c>
+      <c r="F99" t="s">
+        <v>25</v>
+      </c>
+      <c r="G99" t="s">
+        <v>25</v>
+      </c>
+      <c r="H99" t="s">
+        <v>25</v>
+      </c>
+      <c r="I99" t="s">
+        <v>25</v>
+      </c>
+      <c r="J99" t="s">
+        <v>25</v>
+      </c>
+      <c r="K99" t="s">
+        <v>320</v>
+      </c>
+      <c r="L99" t="s">
+        <v>321</v>
+      </c>
+      <c r="M99" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>322</v>
+      </c>
+      <c r="B100" t="s">
+        <v>323</v>
+      </c>
+      <c r="C100" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" t="s">
+        <v>17</v>
+      </c>
+      <c r="F100" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" t="s">
+        <v>19</v>
+      </c>
+      <c r="H100" t="s">
+        <v>20</v>
+      </c>
+      <c r="I100" t="s">
+        <v>21</v>
+      </c>
+      <c r="J100" t="s">
+        <v>315</v>
+      </c>
+      <c r="K100" t="s">
+        <v>324</v>
+      </c>
+      <c r="L100" t="s">
+        <v>325</v>
+      </c>
+      <c r="M100" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>25</v>
+      </c>
+      <c r="B101" t="s">
+        <v>25</v>
+      </c>
+      <c r="C101" t="s">
+        <v>25</v>
+      </c>
+      <c r="D101" t="s">
+        <v>25</v>
+      </c>
+      <c r="E101" t="s">
+        <v>25</v>
+      </c>
+      <c r="F101" t="s">
+        <v>25</v>
+      </c>
+      <c r="G101" t="s">
+        <v>25</v>
+      </c>
+      <c r="H101" t="s">
+        <v>25</v>
+      </c>
+      <c r="I101" t="s">
+        <v>25</v>
+      </c>
+      <c r="J101" t="s">
+        <v>25</v>
+      </c>
+      <c r="K101" t="s">
+        <v>318</v>
+      </c>
+      <c r="L101" t="s">
+        <v>326</v>
+      </c>
+      <c r="M101" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>25</v>
+      </c>
+      <c r="B102" t="s">
+        <v>25</v>
+      </c>
+      <c r="C102" t="s">
+        <v>25</v>
+      </c>
+      <c r="D102" t="s">
+        <v>25</v>
+      </c>
+      <c r="E102" t="s">
+        <v>25</v>
+      </c>
+      <c r="F102" t="s">
+        <v>25</v>
+      </c>
+      <c r="G102" t="s">
+        <v>25</v>
+      </c>
+      <c r="H102" t="s">
+        <v>25</v>
+      </c>
+      <c r="I102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J102" t="s">
+        <v>25</v>
+      </c>
+      <c r="K102" t="s">
+        <v>320</v>
+      </c>
+      <c r="L102" t="s">
+        <v>327</v>
+      </c>
+      <c r="M102" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>328</v>
+      </c>
+      <c r="B103" t="s">
+        <v>329</v>
+      </c>
+      <c r="C103" t="s">
+        <v>15</v>
+      </c>
+      <c r="D103" t="s">
+        <v>16</v>
+      </c>
+      <c r="E103" t="s">
+        <v>330</v>
+      </c>
+      <c r="F103" t="s">
+        <v>18</v>
+      </c>
+      <c r="G103" t="s">
+        <v>19</v>
+      </c>
+      <c r="H103" t="s">
+        <v>20</v>
+      </c>
+      <c r="I103" t="s">
+        <v>21</v>
+      </c>
+      <c r="J103" t="s">
+        <v>177</v>
+      </c>
+      <c r="K103" t="s">
+        <v>331</v>
+      </c>
+      <c r="L103" t="s">
+        <v>332</v>
+      </c>
+      <c r="M103" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>25</v>
+      </c>
+      <c r="B104" t="s">
+        <v>25</v>
+      </c>
+      <c r="C104" t="s">
+        <v>25</v>
+      </c>
+      <c r="D104" t="s">
+        <v>25</v>
+      </c>
+      <c r="E104" t="s">
+        <v>25</v>
+      </c>
+      <c r="F104" t="s">
+        <v>25</v>
+      </c>
+      <c r="G104" t="s">
+        <v>25</v>
+      </c>
+      <c r="H104" t="s">
+        <v>25</v>
+      </c>
+      <c r="I104" t="s">
+        <v>25</v>
+      </c>
+      <c r="J104" t="s">
+        <v>25</v>
+      </c>
+      <c r="K104" t="s">
+        <v>318</v>
+      </c>
+      <c r="L104" t="s">
+        <v>333</v>
+      </c>
+      <c r="M104" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>25</v>
+      </c>
+      <c r="B105" t="s">
+        <v>25</v>
+      </c>
+      <c r="C105" t="s">
+        <v>25</v>
+      </c>
+      <c r="D105" t="s">
+        <v>25</v>
+      </c>
+      <c r="E105" t="s">
+        <v>25</v>
+      </c>
+      <c r="F105" t="s">
+        <v>25</v>
+      </c>
+      <c r="G105" t="s">
+        <v>25</v>
+      </c>
+      <c r="H105" t="s">
+        <v>25</v>
+      </c>
+      <c r="I105" t="s">
+        <v>25</v>
+      </c>
+      <c r="J105" t="s">
+        <v>25</v>
+      </c>
+      <c r="K105" t="s">
+        <v>334</v>
+      </c>
+      <c r="L105" t="s">
+        <v>335</v>
+      </c>
+      <c r="M105" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>340</v>
       </c>
     </row>
   </sheetData>

--- a/clients/encore/testcases/search-for-product-groups/item-search-search-for-product-groups.xlsx
+++ b/clients/encore/testcases/search-for-product-groups/item-search-search-for-product-groups.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="345">
   <si>
     <t>TC ID</t>
   </si>
@@ -433,7 +433,7 @@
     <t>TC-ISR-PGR-016</t>
   </si>
   <si>
-    <t>A search submitted within the typing debounce runs the previous term (known defect)</t>
+    <t>A submit inside the typing debounce runs the previous term; after the pause the typed word runs</t>
   </si>
   <si>
     <t>A fresh page load with a clean search (no executed term stored)</t>
@@ -442,13 +442,25 @@
     <t>1. Click the box, type ZZ E2E by keystrokes and press Enter immediately (no pause)</t>
   </si>
   <si>
-    <t>Intent: the typed term is searched and its groups are found. Today: the empty term is searched — "0 product groups found" with `ZZ E2E` still in the box</t>
-  </si>
-  <si>
-    <t>2. Search ZZ E2E properly (pause before Enter), then select all, type Audio and press Enter at once</t>
-  </si>
-  <si>
-    <t>Intent: the `Audio` groups. Today: the `ZZ E2E` rows stay while the box reads `Audio`</t>
+    <t>The previously committed term runs — on a first visit the empty term: "0 product groups found", no rows, `ZZ E2E` still in the box</t>
+  </si>
+  <si>
+    <t>2. Type ZZ E2E again, pause, and press Enter</t>
+  </si>
+  <si>
+    <t>The `ZZ E2E` groups are found</t>
+  </si>
+  <si>
+    <t>3. Select all, type Audio and press Enter at once</t>
+  </si>
+  <si>
+    <t>The `ZZ E2E` rows and count stay while the box reads `Audio`</t>
+  </si>
+  <si>
+    <t>4. Type Audio again, pause, and press Enter</t>
+  </si>
+  <si>
+    <t>The `Audio` groups replace the rows</t>
   </si>
   <si>
     <t>TC-ISR-PGR-017</t>
@@ -785,7 +797,7 @@
     <t>1. Read the Name column on page 1</t>
   </si>
   <si>
-    <t>Every name is ≤ the next one (ascending by character code — `&lt;` sorts before `A`)</t>
+    <t>Every name is ≤ the next one (ascending with letter case ignored — `&lt;` sorts before `A`)</t>
   </si>
   <si>
     <t>2. Read the header markers</t>
@@ -1442,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3058,40 +3070,40 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" t="s">
+        <v>25</v>
+      </c>
+      <c r="G40" t="s">
+        <v>25</v>
+      </c>
+      <c r="H40" t="s">
+        <v>25</v>
+      </c>
+      <c r="I40" t="s">
+        <v>25</v>
+      </c>
+      <c r="J40" t="s">
+        <v>25</v>
+      </c>
+      <c r="K40" t="s">
         <v>144</v>
       </c>
-      <c r="B40" t="s">
+      <c r="L40" t="s">
         <v>145</v>
-      </c>
-      <c r="C40" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" t="s">
-        <v>16</v>
-      </c>
-      <c r="E40" t="s">
-        <v>17</v>
-      </c>
-      <c r="F40" t="s">
-        <v>18</v>
-      </c>
-      <c r="G40" t="s">
-        <v>19</v>
-      </c>
-      <c r="H40" t="s">
-        <v>20</v>
-      </c>
-      <c r="I40" t="s">
-        <v>21</v>
-      </c>
-      <c r="J40" t="s">
-        <v>146</v>
-      </c>
-      <c r="K40" t="s">
-        <v>147</v>
-      </c>
-      <c r="L40" t="s">
-        <v>148</v>
       </c>
       <c r="M40" t="s">
         <v>25</v>
@@ -3129,10 +3141,10 @@
         <v>25</v>
       </c>
       <c r="K41" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L41" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="M41" t="s">
         <v>25</v>
@@ -3140,10 +3152,10 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B42" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C42" t="s">
         <v>15</v>
@@ -3167,13 +3179,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="K42" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L42" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M42" t="s">
         <v>25</v>
@@ -3211,10 +3223,10 @@
         <v>25</v>
       </c>
       <c r="K43" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L43" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="M43" t="s">
         <v>25</v>
@@ -3222,10 +3234,10 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B44" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C44" t="s">
         <v>15</v>
@@ -3249,13 +3261,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K44" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L44" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="M44" t="s">
         <v>25</v>
@@ -3293,10 +3305,10 @@
         <v>25</v>
       </c>
       <c r="K45" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="L45" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="M45" t="s">
         <v>25</v>
@@ -3304,34 +3316,34 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>25</v>
+        <v>162</v>
       </c>
       <c r="B46" t="s">
-        <v>25</v>
+        <v>163</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G46" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H46" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I46" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J46" t="s">
-        <v>25</v>
+        <v>164</v>
       </c>
       <c r="K46" t="s">
         <v>165</v>
@@ -3345,40 +3357,40 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" t="s">
+        <v>25</v>
+      </c>
+      <c r="H47" t="s">
+        <v>25</v>
+      </c>
+      <c r="I47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K47" t="s">
         <v>167</v>
       </c>
-      <c r="B47" t="s">
+      <c r="L47" t="s">
         <v>168</v>
-      </c>
-      <c r="C47" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" t="s">
-        <v>16</v>
-      </c>
-      <c r="E47" t="s">
-        <v>169</v>
-      </c>
-      <c r="F47" t="s">
-        <v>18</v>
-      </c>
-      <c r="G47" t="s">
-        <v>19</v>
-      </c>
-      <c r="H47" t="s">
-        <v>20</v>
-      </c>
-      <c r="I47" t="s">
-        <v>21</v>
-      </c>
-      <c r="J47" t="s">
-        <v>170</v>
-      </c>
-      <c r="K47" t="s">
-        <v>171</v>
-      </c>
-      <c r="L47" t="s">
-        <v>172</v>
       </c>
       <c r="M47" t="s">
         <v>25</v>
@@ -3416,10 +3428,10 @@
         <v>25</v>
       </c>
       <c r="K48" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L48" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M48" t="s">
         <v>25</v>
@@ -3427,10 +3439,10 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B49" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C49" t="s">
         <v>15</v>
@@ -3439,7 +3451,7 @@
         <v>16</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>173</v>
       </c>
       <c r="F49" t="s">
         <v>18</v>
@@ -3454,13 +3466,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K49" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="L49" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M49" t="s">
         <v>25</v>
@@ -3498,10 +3510,10 @@
         <v>25</v>
       </c>
       <c r="K50" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="L50" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="M50" t="s">
         <v>25</v>
@@ -3509,34 +3521,34 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>25</v>
+        <v>179</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="C51" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E51" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F51" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G51" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H51" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I51" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J51" t="s">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="K51" t="s">
         <v>182</v>
@@ -3591,40 +3603,40 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" t="s">
+        <v>25</v>
+      </c>
+      <c r="H53" t="s">
+        <v>25</v>
+      </c>
+      <c r="I53" t="s">
+        <v>25</v>
+      </c>
+      <c r="J53" t="s">
+        <v>25</v>
+      </c>
+      <c r="K53" t="s">
         <v>186</v>
       </c>
-      <c r="B53" t="s">
+      <c r="L53" t="s">
         <v>187</v>
-      </c>
-      <c r="C53" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" t="s">
-        <v>16</v>
-      </c>
-      <c r="E53" t="s">
-        <v>17</v>
-      </c>
-      <c r="F53" t="s">
-        <v>18</v>
-      </c>
-      <c r="G53" t="s">
-        <v>19</v>
-      </c>
-      <c r="H53" t="s">
-        <v>20</v>
-      </c>
-      <c r="I53" t="s">
-        <v>21</v>
-      </c>
-      <c r="J53" t="s">
-        <v>91</v>
-      </c>
-      <c r="K53" t="s">
-        <v>188</v>
-      </c>
-      <c r="L53" t="s">
-        <v>189</v>
       </c>
       <c r="M53" t="s">
         <v>25</v>
@@ -3662,10 +3674,10 @@
         <v>25</v>
       </c>
       <c r="K54" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L54" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M54" t="s">
         <v>25</v>
@@ -3673,10 +3685,10 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B55" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C55" t="s">
         <v>15</v>
@@ -3685,7 +3697,7 @@
         <v>16</v>
       </c>
       <c r="E55" t="s">
-        <v>194</v>
+        <v>17</v>
       </c>
       <c r="F55" t="s">
         <v>18</v>
@@ -3700,13 +3712,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="s">
-        <v>195</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L55" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M55" t="s">
         <v>25</v>
@@ -3744,10 +3756,10 @@
         <v>25</v>
       </c>
       <c r="K56" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="L56" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="M56" t="s">
         <v>25</v>
@@ -3755,10 +3767,10 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B57" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C57" t="s">
         <v>15</v>
@@ -3767,7 +3779,7 @@
         <v>16</v>
       </c>
       <c r="E57" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F57" t="s">
         <v>18</v>
@@ -3782,13 +3794,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="K57" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="L57" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="M57" t="s">
         <v>25</v>
@@ -3826,10 +3838,10 @@
         <v>25</v>
       </c>
       <c r="K58" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="L58" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="M58" t="s">
         <v>25</v>
@@ -3837,40 +3849,40 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>25</v>
+        <v>204</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>205</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D59" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E59" t="s">
-        <v>25</v>
+        <v>206</v>
       </c>
       <c r="F59" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G59" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H59" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I59" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J59" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="K59" t="s">
-        <v>52</v>
+        <v>208</v>
       </c>
       <c r="L59" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M59" t="s">
         <v>25</v>
@@ -3878,40 +3890,40 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>209</v>
+        <v>25</v>
       </c>
       <c r="B60" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" t="s">
+        <v>25</v>
+      </c>
+      <c r="D60" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" t="s">
+        <v>25</v>
+      </c>
+      <c r="G60" t="s">
+        <v>25</v>
+      </c>
+      <c r="H60" t="s">
+        <v>25</v>
+      </c>
+      <c r="I60" t="s">
+        <v>25</v>
+      </c>
+      <c r="J60" t="s">
+        <v>25</v>
+      </c>
+      <c r="K60" t="s">
         <v>210</v>
       </c>
-      <c r="C60" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" t="s">
-        <v>16</v>
-      </c>
-      <c r="E60" t="s">
-        <v>17</v>
-      </c>
-      <c r="F60" t="s">
-        <v>18</v>
-      </c>
-      <c r="G60" t="s">
-        <v>19</v>
-      </c>
-      <c r="H60" t="s">
-        <v>20</v>
-      </c>
-      <c r="I60" t="s">
-        <v>21</v>
-      </c>
-      <c r="J60" t="s">
+      <c r="L60" t="s">
         <v>211</v>
-      </c>
-      <c r="K60" t="s">
-        <v>212</v>
-      </c>
-      <c r="L60" t="s">
-        <v>213</v>
       </c>
       <c r="M60" t="s">
         <v>25</v>
@@ -3949,10 +3961,10 @@
         <v>25</v>
       </c>
       <c r="K61" t="s">
-        <v>214</v>
+        <v>52</v>
       </c>
       <c r="L61" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M61" t="s">
         <v>25</v>
@@ -3960,34 +3972,34 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>25</v>
+        <v>213</v>
       </c>
       <c r="B62" t="s">
-        <v>25</v>
+        <v>214</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E62" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F62" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G62" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H62" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I62" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J62" t="s">
-        <v>25</v>
+        <v>215</v>
       </c>
       <c r="K62" t="s">
         <v>216</v>
@@ -4083,40 +4095,40 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" t="s">
+        <v>25</v>
+      </c>
+      <c r="C65" t="s">
+        <v>25</v>
+      </c>
+      <c r="D65" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" t="s">
+        <v>25</v>
+      </c>
+      <c r="G65" t="s">
+        <v>25</v>
+      </c>
+      <c r="H65" t="s">
+        <v>25</v>
+      </c>
+      <c r="I65" t="s">
+        <v>25</v>
+      </c>
+      <c r="J65" t="s">
+        <v>25</v>
+      </c>
+      <c r="K65" t="s">
         <v>222</v>
       </c>
-      <c r="B65" t="s">
+      <c r="L65" t="s">
         <v>223</v>
-      </c>
-      <c r="C65" t="s">
-        <v>15</v>
-      </c>
-      <c r="D65" t="s">
-        <v>16</v>
-      </c>
-      <c r="E65" t="s">
-        <v>17</v>
-      </c>
-      <c r="F65" t="s">
-        <v>18</v>
-      </c>
-      <c r="G65" t="s">
-        <v>19</v>
-      </c>
-      <c r="H65" t="s">
-        <v>20</v>
-      </c>
-      <c r="I65" t="s">
-        <v>21</v>
-      </c>
-      <c r="J65" t="s">
-        <v>224</v>
-      </c>
-      <c r="K65" t="s">
-        <v>225</v>
-      </c>
-      <c r="L65" t="s">
-        <v>226</v>
       </c>
       <c r="M65" t="s">
         <v>25</v>
@@ -4154,10 +4166,10 @@
         <v>25</v>
       </c>
       <c r="K66" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L66" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="M66" t="s">
         <v>25</v>
@@ -4165,34 +4177,34 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>25</v>
+        <v>226</v>
       </c>
       <c r="B67" t="s">
-        <v>25</v>
+        <v>227</v>
       </c>
       <c r="C67" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E67" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F67" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G67" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H67" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I67" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J67" t="s">
-        <v>25</v>
+        <v>228</v>
       </c>
       <c r="K67" t="s">
         <v>229</v>
@@ -4247,40 +4259,40 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>25</v>
+      </c>
+      <c r="B69" t="s">
+        <v>25</v>
+      </c>
+      <c r="C69" t="s">
+        <v>25</v>
+      </c>
+      <c r="D69" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" t="s">
+        <v>25</v>
+      </c>
+      <c r="G69" t="s">
+        <v>25</v>
+      </c>
+      <c r="H69" t="s">
+        <v>25</v>
+      </c>
+      <c r="I69" t="s">
+        <v>25</v>
+      </c>
+      <c r="J69" t="s">
+        <v>25</v>
+      </c>
+      <c r="K69" t="s">
         <v>233</v>
       </c>
-      <c r="B69" t="s">
+      <c r="L69" t="s">
         <v>234</v>
-      </c>
-      <c r="C69" t="s">
-        <v>15</v>
-      </c>
-      <c r="D69" t="s">
-        <v>16</v>
-      </c>
-      <c r="E69" t="s">
-        <v>194</v>
-      </c>
-      <c r="F69" t="s">
-        <v>18</v>
-      </c>
-      <c r="G69" t="s">
-        <v>19</v>
-      </c>
-      <c r="H69" t="s">
-        <v>20</v>
-      </c>
-      <c r="I69" t="s">
-        <v>21</v>
-      </c>
-      <c r="J69" t="s">
-        <v>235</v>
-      </c>
-      <c r="K69" t="s">
-        <v>236</v>
-      </c>
-      <c r="L69" t="s">
-        <v>237</v>
       </c>
       <c r="M69" t="s">
         <v>25</v>
@@ -4318,10 +4330,10 @@
         <v>25</v>
       </c>
       <c r="K70" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="L70" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="M70" t="s">
         <v>25</v>
@@ -4329,34 +4341,34 @@
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>25</v>
+        <v>237</v>
       </c>
       <c r="B71" t="s">
-        <v>25</v>
+        <v>238</v>
       </c>
       <c r="C71" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E71" t="s">
-        <v>25</v>
+        <v>198</v>
       </c>
       <c r="F71" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G71" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H71" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I71" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J71" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="K71" t="s">
         <v>240</v>
@@ -4370,40 +4382,40 @@
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>25</v>
+      </c>
+      <c r="B72" t="s">
+        <v>25</v>
+      </c>
+      <c r="C72" t="s">
+        <v>25</v>
+      </c>
+      <c r="D72" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" t="s">
+        <v>25</v>
+      </c>
+      <c r="F72" t="s">
+        <v>25</v>
+      </c>
+      <c r="G72" t="s">
+        <v>25</v>
+      </c>
+      <c r="H72" t="s">
+        <v>25</v>
+      </c>
+      <c r="I72" t="s">
+        <v>25</v>
+      </c>
+      <c r="J72" t="s">
+        <v>25</v>
+      </c>
+      <c r="K72" t="s">
         <v>242</v>
       </c>
-      <c r="B72" t="s">
+      <c r="L72" t="s">
         <v>243</v>
-      </c>
-      <c r="C72" t="s">
-        <v>15</v>
-      </c>
-      <c r="D72" t="s">
-        <v>16</v>
-      </c>
-      <c r="E72" t="s">
-        <v>17</v>
-      </c>
-      <c r="F72" t="s">
-        <v>18</v>
-      </c>
-      <c r="G72" t="s">
-        <v>19</v>
-      </c>
-      <c r="H72" t="s">
-        <v>20</v>
-      </c>
-      <c r="I72" t="s">
-        <v>21</v>
-      </c>
-      <c r="J72" t="s">
-        <v>244</v>
-      </c>
-      <c r="K72" t="s">
-        <v>71</v>
-      </c>
-      <c r="L72" t="s">
-        <v>245</v>
       </c>
       <c r="M72" t="s">
         <v>25</v>
@@ -4441,10 +4453,10 @@
         <v>25</v>
       </c>
       <c r="K73" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L73" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M73" t="s">
         <v>25</v>
@@ -4452,10 +4464,10 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B74" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C74" t="s">
         <v>15</v>
@@ -4479,13 +4491,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K74" t="s">
-        <v>251</v>
+        <v>71</v>
       </c>
       <c r="L74" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="M74" t="s">
         <v>25</v>
@@ -4523,10 +4535,10 @@
         <v>25</v>
       </c>
       <c r="K75" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="L75" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="M75" t="s">
         <v>25</v>
@@ -4534,10 +4546,10 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B76" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C76" t="s">
         <v>15</v>
@@ -4561,13 +4573,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="K76" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L76" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M76" t="s">
         <v>25</v>
@@ -4605,10 +4617,10 @@
         <v>25</v>
       </c>
       <c r="K77" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="L77" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="M77" t="s">
         <v>25</v>
@@ -4616,34 +4628,34 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>25</v>
+        <v>259</v>
       </c>
       <c r="B78" t="s">
-        <v>25</v>
+        <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E78" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F78" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G78" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H78" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I78" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J78" t="s">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="K78" t="s">
         <v>261</v>
@@ -4657,40 +4669,40 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79" t="s">
+        <v>25</v>
+      </c>
+      <c r="D79" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" t="s">
+        <v>25</v>
+      </c>
+      <c r="F79" t="s">
+        <v>25</v>
+      </c>
+      <c r="G79" t="s">
+        <v>25</v>
+      </c>
+      <c r="H79" t="s">
+        <v>25</v>
+      </c>
+      <c r="I79" t="s">
+        <v>25</v>
+      </c>
+      <c r="J79" t="s">
+        <v>25</v>
+      </c>
+      <c r="K79" t="s">
         <v>263</v>
       </c>
-      <c r="B79" t="s">
+      <c r="L79" t="s">
         <v>264</v>
-      </c>
-      <c r="C79" t="s">
-        <v>15</v>
-      </c>
-      <c r="D79" t="s">
-        <v>16</v>
-      </c>
-      <c r="E79" t="s">
-        <v>17</v>
-      </c>
-      <c r="F79" t="s">
-        <v>18</v>
-      </c>
-      <c r="G79" t="s">
-        <v>19</v>
-      </c>
-      <c r="H79" t="s">
-        <v>20</v>
-      </c>
-      <c r="I79" t="s">
-        <v>21</v>
-      </c>
-      <c r="J79" t="s">
-        <v>265</v>
-      </c>
-      <c r="K79" t="s">
-        <v>266</v>
-      </c>
-      <c r="L79" t="s">
-        <v>267</v>
       </c>
       <c r="M79" t="s">
         <v>25</v>
@@ -4728,10 +4740,10 @@
         <v>25</v>
       </c>
       <c r="K80" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="L80" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M80" t="s">
         <v>25</v>
@@ -4739,10 +4751,10 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B81" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C81" t="s">
         <v>15</v>
@@ -4766,13 +4778,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="K81" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="L81" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M81" t="s">
         <v>25</v>
@@ -4780,40 +4792,40 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>25</v>
+      </c>
+      <c r="B82" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" t="s">
+        <v>25</v>
+      </c>
+      <c r="D82" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82" t="s">
+        <v>25</v>
+      </c>
+      <c r="F82" t="s">
+        <v>25</v>
+      </c>
+      <c r="G82" t="s">
+        <v>25</v>
+      </c>
+      <c r="H82" t="s">
+        <v>25</v>
+      </c>
+      <c r="I82" t="s">
+        <v>25</v>
+      </c>
+      <c r="J82" t="s">
+        <v>25</v>
+      </c>
+      <c r="K82" t="s">
+        <v>272</v>
+      </c>
+      <c r="L82" t="s">
         <v>273</v>
-      </c>
-      <c r="B82" t="s">
-        <v>274</v>
-      </c>
-      <c r="C82" t="s">
-        <v>15</v>
-      </c>
-      <c r="D82" t="s">
-        <v>16</v>
-      </c>
-      <c r="E82" t="s">
-        <v>17</v>
-      </c>
-      <c r="F82" t="s">
-        <v>18</v>
-      </c>
-      <c r="G82" t="s">
-        <v>19</v>
-      </c>
-      <c r="H82" t="s">
-        <v>20</v>
-      </c>
-      <c r="I82" t="s">
-        <v>21</v>
-      </c>
-      <c r="J82" t="s">
-        <v>275</v>
-      </c>
-      <c r="K82" t="s">
-        <v>276</v>
-      </c>
-      <c r="L82" t="s">
-        <v>277</v>
       </c>
       <c r="M82" t="s">
         <v>25</v>
@@ -4821,40 +4833,40 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>25</v>
+        <v>274</v>
       </c>
       <c r="B83" t="s">
-        <v>25</v>
+        <v>275</v>
       </c>
       <c r="C83" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D83" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E83" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F83" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G83" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H83" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I83" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J83" t="s">
-        <v>25</v>
+        <v>248</v>
       </c>
       <c r="K83" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="L83" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="M83" t="s">
         <v>25</v>
@@ -4862,34 +4874,34 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>25</v>
+        <v>277</v>
       </c>
       <c r="B84" t="s">
-        <v>25</v>
+        <v>278</v>
       </c>
       <c r="C84" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E84" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F84" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G84" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H84" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I84" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J84" t="s">
-        <v>25</v>
+        <v>279</v>
       </c>
       <c r="K84" t="s">
         <v>280</v>
@@ -4944,40 +4956,40 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B86" t="s">
+        <v>25</v>
+      </c>
+      <c r="C86" t="s">
+        <v>25</v>
+      </c>
+      <c r="D86" t="s">
+        <v>25</v>
+      </c>
+      <c r="E86" t="s">
+        <v>25</v>
+      </c>
+      <c r="F86" t="s">
+        <v>25</v>
+      </c>
+      <c r="G86" t="s">
+        <v>25</v>
+      </c>
+      <c r="H86" t="s">
+        <v>25</v>
+      </c>
+      <c r="I86" t="s">
+        <v>25</v>
+      </c>
+      <c r="J86" t="s">
+        <v>25</v>
+      </c>
+      <c r="K86" t="s">
         <v>284</v>
       </c>
-      <c r="B86" t="s">
+      <c r="L86" t="s">
         <v>285</v>
-      </c>
-      <c r="C86" t="s">
-        <v>15</v>
-      </c>
-      <c r="D86" t="s">
-        <v>16</v>
-      </c>
-      <c r="E86" t="s">
-        <v>17</v>
-      </c>
-      <c r="F86" t="s">
-        <v>18</v>
-      </c>
-      <c r="G86" t="s">
-        <v>19</v>
-      </c>
-      <c r="H86" t="s">
-        <v>20</v>
-      </c>
-      <c r="I86" t="s">
-        <v>21</v>
-      </c>
-      <c r="J86" t="s">
-        <v>177</v>
-      </c>
-      <c r="K86" t="s">
-        <v>286</v>
-      </c>
-      <c r="L86" t="s">
-        <v>287</v>
       </c>
       <c r="M86" t="s">
         <v>25</v>
@@ -5015,10 +5027,10 @@
         <v>25</v>
       </c>
       <c r="K87" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="L87" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="M87" t="s">
         <v>25</v>
@@ -5026,34 +5038,34 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="B88" t="s">
-        <v>25</v>
+        <v>289</v>
       </c>
       <c r="C88" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E88" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F88" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G88" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H88" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I88" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J88" t="s">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="K88" t="s">
         <v>290</v>
@@ -5108,40 +5120,40 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>25</v>
+      </c>
+      <c r="B90" t="s">
+        <v>25</v>
+      </c>
+      <c r="C90" t="s">
+        <v>25</v>
+      </c>
+      <c r="D90" t="s">
+        <v>25</v>
+      </c>
+      <c r="E90" t="s">
+        <v>25</v>
+      </c>
+      <c r="F90" t="s">
+        <v>25</v>
+      </c>
+      <c r="G90" t="s">
+        <v>25</v>
+      </c>
+      <c r="H90" t="s">
+        <v>25</v>
+      </c>
+      <c r="I90" t="s">
+        <v>25</v>
+      </c>
+      <c r="J90" t="s">
+        <v>25</v>
+      </c>
+      <c r="K90" t="s">
         <v>294</v>
       </c>
-      <c r="B90" t="s">
+      <c r="L90" t="s">
         <v>295</v>
-      </c>
-      <c r="C90" t="s">
-        <v>15</v>
-      </c>
-      <c r="D90" t="s">
-        <v>16</v>
-      </c>
-      <c r="E90" t="s">
-        <v>17</v>
-      </c>
-      <c r="F90" t="s">
-        <v>18</v>
-      </c>
-      <c r="G90" t="s">
-        <v>19</v>
-      </c>
-      <c r="H90" t="s">
-        <v>20</v>
-      </c>
-      <c r="I90" t="s">
-        <v>21</v>
-      </c>
-      <c r="J90" t="s">
-        <v>296</v>
-      </c>
-      <c r="K90" t="s">
-        <v>297</v>
-      </c>
-      <c r="L90" t="s">
-        <v>298</v>
       </c>
       <c r="M90" t="s">
         <v>25</v>
@@ -5179,10 +5191,10 @@
         <v>25</v>
       </c>
       <c r="K91" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="L91" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="M91" t="s">
         <v>25</v>
@@ -5190,40 +5202,40 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>25</v>
+        <v>298</v>
       </c>
       <c r="B92" t="s">
-        <v>25</v>
+        <v>299</v>
       </c>
       <c r="C92" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E92" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F92" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G92" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H92" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I92" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J92" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="K92" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="L92" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M92" t="s">
         <v>25</v>
@@ -5261,10 +5273,10 @@
         <v>25</v>
       </c>
       <c r="K93" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L93" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M93" t="s">
         <v>25</v>
@@ -5302,7 +5314,7 @@
         <v>25</v>
       </c>
       <c r="K94" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="L94" t="s">
         <v>305</v>
@@ -5313,40 +5325,40 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>25</v>
+      </c>
+      <c r="B95" t="s">
+        <v>25</v>
+      </c>
+      <c r="C95" t="s">
+        <v>25</v>
+      </c>
+      <c r="D95" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95" t="s">
+        <v>25</v>
+      </c>
+      <c r="F95" t="s">
+        <v>25</v>
+      </c>
+      <c r="G95" t="s">
+        <v>25</v>
+      </c>
+      <c r="H95" t="s">
+        <v>25</v>
+      </c>
+      <c r="I95" t="s">
+        <v>25</v>
+      </c>
+      <c r="J95" t="s">
+        <v>25</v>
+      </c>
+      <c r="K95" t="s">
         <v>306</v>
       </c>
-      <c r="B95" t="s">
+      <c r="L95" t="s">
         <v>307</v>
-      </c>
-      <c r="C95" t="s">
-        <v>15</v>
-      </c>
-      <c r="D95" t="s">
-        <v>16</v>
-      </c>
-      <c r="E95" t="s">
-        <v>17</v>
-      </c>
-      <c r="F95" t="s">
-        <v>18</v>
-      </c>
-      <c r="G95" t="s">
-        <v>19</v>
-      </c>
-      <c r="H95" t="s">
-        <v>20</v>
-      </c>
-      <c r="I95" t="s">
-        <v>21</v>
-      </c>
-      <c r="J95" t="s">
-        <v>308</v>
-      </c>
-      <c r="K95" t="s">
-        <v>309</v>
-      </c>
-      <c r="L95" t="s">
-        <v>310</v>
       </c>
       <c r="M95" t="s">
         <v>25</v>
@@ -5384,10 +5396,10 @@
         <v>25</v>
       </c>
       <c r="K96" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L96" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="M96" t="s">
         <v>25</v>
@@ -5395,10 +5407,10 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B97" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C97" t="s">
         <v>15</v>
@@ -5422,13 +5434,13 @@
         <v>21</v>
       </c>
       <c r="J97" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="K97" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="L97" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="M97" t="s">
         <v>25</v>
@@ -5466,10 +5478,10 @@
         <v>25</v>
       </c>
       <c r="K98" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L98" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="M98" t="s">
         <v>25</v>
@@ -5477,34 +5489,34 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>25</v>
+        <v>317</v>
       </c>
       <c r="B99" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="C99" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D99" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E99" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F99" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G99" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H99" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I99" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J99" t="s">
-        <v>25</v>
+        <v>319</v>
       </c>
       <c r="K99" t="s">
         <v>320</v>
@@ -5518,40 +5530,40 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>25</v>
+      </c>
+      <c r="B100" t="s">
+        <v>25</v>
+      </c>
+      <c r="C100" t="s">
+        <v>25</v>
+      </c>
+      <c r="D100" t="s">
+        <v>25</v>
+      </c>
+      <c r="E100" t="s">
+        <v>25</v>
+      </c>
+      <c r="F100" t="s">
+        <v>25</v>
+      </c>
+      <c r="G100" t="s">
+        <v>25</v>
+      </c>
+      <c r="H100" t="s">
+        <v>25</v>
+      </c>
+      <c r="I100" t="s">
+        <v>25</v>
+      </c>
+      <c r="J100" t="s">
+        <v>25</v>
+      </c>
+      <c r="K100" t="s">
         <v>322</v>
       </c>
-      <c r="B100" t="s">
+      <c r="L100" t="s">
         <v>323</v>
-      </c>
-      <c r="C100" t="s">
-        <v>15</v>
-      </c>
-      <c r="D100" t="s">
-        <v>16</v>
-      </c>
-      <c r="E100" t="s">
-        <v>17</v>
-      </c>
-      <c r="F100" t="s">
-        <v>18</v>
-      </c>
-      <c r="G100" t="s">
-        <v>19</v>
-      </c>
-      <c r="H100" t="s">
-        <v>20</v>
-      </c>
-      <c r="I100" t="s">
-        <v>21</v>
-      </c>
-      <c r="J100" t="s">
-        <v>315</v>
-      </c>
-      <c r="K100" t="s">
-        <v>324</v>
-      </c>
-      <c r="L100" t="s">
-        <v>325</v>
       </c>
       <c r="M100" t="s">
         <v>25</v>
@@ -5589,10 +5601,10 @@
         <v>25</v>
       </c>
       <c r="K101" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="L101" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M101" t="s">
         <v>25</v>
@@ -5600,40 +5612,40 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>25</v>
+        <v>326</v>
       </c>
       <c r="B102" t="s">
-        <v>25</v>
+        <v>327</v>
       </c>
       <c r="C102" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D102" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E102" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F102" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G102" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H102" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I102" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J102" t="s">
-        <v>25</v>
+        <v>319</v>
       </c>
       <c r="K102" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="L102" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M102" t="s">
         <v>25</v>
@@ -5641,40 +5653,40 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>328</v>
+        <v>25</v>
       </c>
       <c r="B103" t="s">
-        <v>329</v>
+        <v>25</v>
       </c>
       <c r="C103" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D103" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E103" t="s">
+        <v>25</v>
+      </c>
+      <c r="F103" t="s">
+        <v>25</v>
+      </c>
+      <c r="G103" t="s">
+        <v>25</v>
+      </c>
+      <c r="H103" t="s">
+        <v>25</v>
+      </c>
+      <c r="I103" t="s">
+        <v>25</v>
+      </c>
+      <c r="J103" t="s">
+        <v>25</v>
+      </c>
+      <c r="K103" t="s">
+        <v>322</v>
+      </c>
+      <c r="L103" t="s">
         <v>330</v>
-      </c>
-      <c r="F103" t="s">
-        <v>18</v>
-      </c>
-      <c r="G103" t="s">
-        <v>19</v>
-      </c>
-      <c r="H103" t="s">
-        <v>20</v>
-      </c>
-      <c r="I103" t="s">
-        <v>21</v>
-      </c>
-      <c r="J103" t="s">
-        <v>177</v>
-      </c>
-      <c r="K103" t="s">
-        <v>331</v>
-      </c>
-      <c r="L103" t="s">
-        <v>332</v>
       </c>
       <c r="M103" t="s">
         <v>25</v>
@@ -5712,10 +5724,10 @@
         <v>25</v>
       </c>
       <c r="K104" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="L104" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M104" t="s">
         <v>25</v>
@@ -5723,84 +5735,166 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>25</v>
+        <v>332</v>
       </c>
       <c r="B105" t="s">
-        <v>25</v>
+        <v>333</v>
       </c>
       <c r="C105" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D105" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E105" t="s">
-        <v>25</v>
+        <v>334</v>
       </c>
       <c r="F105" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G105" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H105" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I105" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J105" t="s">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="K105" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L105" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M105" t="s">
         <v>25</v>
       </c>
     </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>25</v>
+      </c>
+      <c r="B106" t="s">
+        <v>25</v>
+      </c>
+      <c r="C106" t="s">
+        <v>25</v>
+      </c>
+      <c r="D106" t="s">
+        <v>25</v>
+      </c>
+      <c r="E106" t="s">
+        <v>25</v>
+      </c>
+      <c r="F106" t="s">
+        <v>25</v>
+      </c>
+      <c r="G106" t="s">
+        <v>25</v>
+      </c>
+      <c r="H106" t="s">
+        <v>25</v>
+      </c>
+      <c r="I106" t="s">
+        <v>25</v>
+      </c>
+      <c r="J106" t="s">
+        <v>25</v>
+      </c>
+      <c r="K106" t="s">
+        <v>322</v>
+      </c>
+      <c r="L106" t="s">
+        <v>337</v>
+      </c>
+      <c r="M106" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H107" s="2" t="s">
+      <c r="A107" t="s">
+        <v>25</v>
+      </c>
+      <c r="B107" t="s">
+        <v>25</v>
+      </c>
+      <c r="C107" t="s">
+        <v>25</v>
+      </c>
+      <c r="D107" t="s">
+        <v>25</v>
+      </c>
+      <c r="E107" t="s">
+        <v>25</v>
+      </c>
+      <c r="F107" t="s">
+        <v>25</v>
+      </c>
+      <c r="G107" t="s">
+        <v>25</v>
+      </c>
+      <c r="H107" t="s">
+        <v>25</v>
+      </c>
+      <c r="I107" t="s">
+        <v>25</v>
+      </c>
+      <c r="J107" t="s">
+        <v>25</v>
+      </c>
+      <c r="K107" t="s">
         <v>338</v>
       </c>
-      <c r="I107" s="2" t="s">
+      <c r="L107" t="s">
         <v>339</v>
       </c>
-      <c r="J107" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K107" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L107" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M107" s="2" t="s">
+      <c r="M107" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
         <v>340</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>344</v>
       </c>
     </row>
   </sheetData>
